--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>BRAKE</t>
   </si>
@@ -180,10 +180,64 @@
     <t>Item.Equipment.Description.Ccc</t>
   </si>
   <si>
+    <t>Item.Equipment.Description.CursedTwinScythes</t>
+  </si>
+  <si>
     <t>Item.Equipment.Description.Ddd</t>
   </si>
   <si>
+    <t>Item.Equipment.Description.DullAxe</t>
+  </si>
+  <si>
     <t>Item.Equipment.Description.Eee</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.FocusAmber</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.GreenCrystal</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HarvestGem</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HeavyBlade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.HeavyPickaxe</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.LevitationClothes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.MysteriousJade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.PatchShoes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.PsychicPearl</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.RippleArmband</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.RoundShield</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.SlaughterMask</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.SmartKey</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.ThunderHeadpiece</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.TightHelmet</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Description.WisdomStaff</t>
   </si>
   <si>
     <t>Item.Equipment.Name.Aaa</t>
@@ -195,10 +249,64 @@
     <t>Item.Equipment.Name.Ccc</t>
   </si>
   <si>
+    <t>Item.Equipment.Name.CursedTwinScythes</t>
+  </si>
+  <si>
     <t>Item.Equipment.Name.Ddd</t>
   </si>
   <si>
+    <t>Item.Equipment.Name.DullAxe</t>
+  </si>
+  <si>
     <t>Item.Equipment.Name.Eee</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.FocusAmber</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.GreenCrystal</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HarvestGem</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HeavyBlade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.HeavyPickaxe</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.LevitationClothes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.MysteriousJade</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.PatchShoes</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.PsychicPearl</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.RippleArmband</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.RoundShield</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.SlaughterMask</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.SmartKey</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.ThunderHeadpiece</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.TightHelmet</t>
+  </si>
+  <si>
+    <t>Item.Equipment.Name.WisdomStaff</t>
   </si>
   <si>
     <t>Item.Material.Description.Aaa</t>
@@ -719,7 +827,83 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp131.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp132.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp133.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp134.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp135.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp136.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp137.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp138.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp139.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp140.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp141.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp142.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp143.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp144.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp145.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp146.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp147.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp148.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp149.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -727,7 +911,75 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp150.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp151.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp152.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp153.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp154.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp155.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp156.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp157.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp158.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp159.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp160.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp161.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp162.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp163.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp164.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp165.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp166.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -3810,6 +4062,1190 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3826,10 +5262,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1143">
+            <xdr:cNvPr hidden="1" name="A1" id="1191">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
+                  <a14:compatExt spid="_x0000_s1191"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3912,10 +5348,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1144">
+            <xdr:cNvPr hidden="1" name="A2" id="1192">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+                  <a14:compatExt spid="_x0000_s1192"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3998,10 +5434,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1145">
+            <xdr:cNvPr hidden="1" name="A3" id="1193">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+                  <a14:compatExt spid="_x0000_s1193"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4084,10 +5520,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1146">
+            <xdr:cNvPr hidden="1" name="A4" id="1194">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
+                  <a14:compatExt spid="_x0000_s1194"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4170,10 +5606,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1147">
+            <xdr:cNvPr hidden="1" name="A5" id="1195">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
+                  <a14:compatExt spid="_x0000_s1195"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4256,10 +5692,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1148">
+            <xdr:cNvPr hidden="1" name="A6" id="1196">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
+                  <a14:compatExt spid="_x0000_s1196"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4342,10 +5778,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1149">
+            <xdr:cNvPr hidden="1" name="A7" id="1197">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+                  <a14:compatExt spid="_x0000_s1197"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4428,10 +5864,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1150">
+            <xdr:cNvPr hidden="1" name="A8" id="1198">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+                  <a14:compatExt spid="_x0000_s1198"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4514,10 +5950,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1151">
+            <xdr:cNvPr hidden="1" name="A9" id="1199">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+                  <a14:compatExt spid="_x0000_s1199"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4600,10 +6036,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1152">
+            <xdr:cNvPr hidden="1" name="A10" id="1200">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
+                  <a14:compatExt spid="_x0000_s1200"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4686,10 +6122,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1153">
+            <xdr:cNvPr hidden="1" name="A11" id="1201">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
+                  <a14:compatExt spid="_x0000_s1201"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4772,10 +6208,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1154">
+            <xdr:cNvPr hidden="1" name="A12" id="1202">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1202"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4858,10 +6294,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1155">
+            <xdr:cNvPr hidden="1" name="A13" id="1203">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
+                  <a14:compatExt spid="_x0000_s1203"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4944,10 +6380,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1156">
+            <xdr:cNvPr hidden="1" name="A14" id="1204">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
+                  <a14:compatExt spid="_x0000_s1204"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5030,10 +6466,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1157">
+            <xdr:cNvPr hidden="1" name="A15" id="1205">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
+                  <a14:compatExt spid="_x0000_s1205"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5116,10 +6552,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1158">
+            <xdr:cNvPr hidden="1" name="A16" id="1206">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1158"/>
+                  <a14:compatExt spid="_x0000_s1206"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5202,10 +6638,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1159">
+            <xdr:cNvPr hidden="1" name="A17" id="1207">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1159"/>
+                  <a14:compatExt spid="_x0000_s1207"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5288,10 +6724,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1160">
+            <xdr:cNvPr hidden="1" name="A18" id="1208">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1160"/>
+                  <a14:compatExt spid="_x0000_s1208"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5374,10 +6810,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1161">
+            <xdr:cNvPr hidden="1" name="A19" id="1209">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1161"/>
+                  <a14:compatExt spid="_x0000_s1209"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5460,10 +6896,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1162">
+            <xdr:cNvPr hidden="1" name="A20" id="1210">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1162"/>
+                  <a14:compatExt spid="_x0000_s1210"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5546,10 +6982,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1163">
+            <xdr:cNvPr hidden="1" name="A21" id="1211">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1163"/>
+                  <a14:compatExt spid="_x0000_s1211"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5632,10 +7068,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1164">
+            <xdr:cNvPr hidden="1" name="A22" id="1212">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
+                  <a14:compatExt spid="_x0000_s1212"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5718,10 +7154,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1165">
+            <xdr:cNvPr hidden="1" name="A23" id="1213">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1165"/>
+                  <a14:compatExt spid="_x0000_s1213"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5804,10 +7240,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1166">
+            <xdr:cNvPr hidden="1" name="A24" id="1214">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1166"/>
+                  <a14:compatExt spid="_x0000_s1214"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5890,10 +7326,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1167">
+            <xdr:cNvPr hidden="1" name="A25" id="1215">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1167"/>
+                  <a14:compatExt spid="_x0000_s1215"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5976,10 +7412,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1168">
+            <xdr:cNvPr hidden="1" name="A26" id="1216">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1168"/>
+                  <a14:compatExt spid="_x0000_s1216"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6062,10 +7498,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1169">
+            <xdr:cNvPr hidden="1" name="A27" id="1217">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1169"/>
+                  <a14:compatExt spid="_x0000_s1217"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6148,10 +7584,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1170">
+            <xdr:cNvPr hidden="1" name="A28" id="1218">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1170"/>
+                  <a14:compatExt spid="_x0000_s1218"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6234,10 +7670,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1171">
+            <xdr:cNvPr hidden="1" name="A29" id="1219">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1171"/>
+                  <a14:compatExt spid="_x0000_s1219"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6320,10 +7756,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1172">
+            <xdr:cNvPr hidden="1" name="A30" id="1220">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1172"/>
+                  <a14:compatExt spid="_x0000_s1220"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6406,10 +7842,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1173">
+            <xdr:cNvPr hidden="1" name="A31" id="1221">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1173"/>
+                  <a14:compatExt spid="_x0000_s1221"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6492,10 +7928,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1174">
+            <xdr:cNvPr hidden="1" name="A32" id="1222">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1174"/>
+                  <a14:compatExt spid="_x0000_s1222"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6578,10 +8014,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1175">
+            <xdr:cNvPr hidden="1" name="A33" id="1223">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1175"/>
+                  <a14:compatExt spid="_x0000_s1223"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6664,10 +8100,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1176">
+            <xdr:cNvPr hidden="1" name="A34" id="1224">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1176"/>
+                  <a14:compatExt spid="_x0000_s1224"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6750,10 +8186,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1177">
+            <xdr:cNvPr hidden="1" name="A35" id="1225">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1177"/>
+                  <a14:compatExt spid="_x0000_s1225"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6836,10 +8272,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1178">
+            <xdr:cNvPr hidden="1" name="A36" id="1226">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1178"/>
+                  <a14:compatExt spid="_x0000_s1226"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6922,10 +8358,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1179">
+            <xdr:cNvPr hidden="1" name="A37" id="1227">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1179"/>
+                  <a14:compatExt spid="_x0000_s1227"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7008,10 +8444,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1180">
+            <xdr:cNvPr hidden="1" name="A38" id="1228">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1180"/>
+                  <a14:compatExt spid="_x0000_s1228"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7094,10 +8530,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1181">
+            <xdr:cNvPr hidden="1" name="A39" id="1229">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1181"/>
+                  <a14:compatExt spid="_x0000_s1229"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7180,10 +8616,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1182">
+            <xdr:cNvPr hidden="1" name="A40" id="1230">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1182"/>
+                  <a14:compatExt spid="_x0000_s1230"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7266,10 +8702,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1183">
+            <xdr:cNvPr hidden="1" name="A41" id="1231">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1183"/>
+                  <a14:compatExt spid="_x0000_s1231"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7352,10 +8788,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1184">
+            <xdr:cNvPr hidden="1" name="A42" id="1232">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1184"/>
+                  <a14:compatExt spid="_x0000_s1232"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7438,10 +8874,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1185">
+            <xdr:cNvPr hidden="1" name="A43" id="1233">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1185"/>
+                  <a14:compatExt spid="_x0000_s1233"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7524,10 +8960,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1186">
+            <xdr:cNvPr hidden="1" name="A44" id="1234">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1186"/>
+                  <a14:compatExt spid="_x0000_s1234"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7610,10 +9046,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1187">
+            <xdr:cNvPr hidden="1" name="A45" id="1235">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1187"/>
+                  <a14:compatExt spid="_x0000_s1235"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7696,10 +9132,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1188">
+            <xdr:cNvPr hidden="1" name="A46" id="1236">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1188"/>
+                  <a14:compatExt spid="_x0000_s1236"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7782,10 +9218,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1189">
+            <xdr:cNvPr hidden="1" name="A47" id="1237">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1189"/>
+                  <a14:compatExt spid="_x0000_s1237"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7868,10 +9304,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1190">
+            <xdr:cNvPr hidden="1" name="A48" id="1238">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1190"/>
+                  <a14:compatExt spid="_x0000_s1238"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7954,10 +9390,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1191">
+            <xdr:cNvPr hidden="1" name="A49" id="1239">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1191"/>
+                  <a14:compatExt spid="_x0000_s1239"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8040,10 +9476,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1192">
+            <xdr:cNvPr hidden="1" name="A50" id="1240">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1192"/>
+                  <a14:compatExt spid="_x0000_s1240"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8126,10 +9562,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1193">
+            <xdr:cNvPr hidden="1" name="A51" id="1241">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1193"/>
+                  <a14:compatExt spid="_x0000_s1241"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8212,10 +9648,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1194">
+            <xdr:cNvPr hidden="1" name="A52" id="1242">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1194"/>
+                  <a14:compatExt spid="_x0000_s1242"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8298,10 +9734,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1195">
+            <xdr:cNvPr hidden="1" name="A53" id="1243">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1195"/>
+                  <a14:compatExt spid="_x0000_s1243"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8384,10 +9820,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1196">
+            <xdr:cNvPr hidden="1" name="A54" id="1244">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1196"/>
+                  <a14:compatExt spid="_x0000_s1244"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8470,10 +9906,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1197">
+            <xdr:cNvPr hidden="1" name="A55" id="1245">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1197"/>
+                  <a14:compatExt spid="_x0000_s1245"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8556,10 +9992,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1198">
+            <xdr:cNvPr hidden="1" name="A56" id="1246">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1198"/>
+                  <a14:compatExt spid="_x0000_s1246"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8642,10 +10078,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1199">
+            <xdr:cNvPr hidden="1" name="A57" id="1247">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1199"/>
+                  <a14:compatExt spid="_x0000_s1247"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8728,10 +10164,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1200">
+            <xdr:cNvPr hidden="1" name="A58" id="1248">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1200"/>
+                  <a14:compatExt spid="_x0000_s1248"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8814,10 +10250,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1201">
+            <xdr:cNvPr hidden="1" name="A59" id="1249">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1201"/>
+                  <a14:compatExt spid="_x0000_s1249"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8900,10 +10336,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1202">
+            <xdr:cNvPr hidden="1" name="A60" id="1250">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1202"/>
+                  <a14:compatExt spid="_x0000_s1250"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8986,10 +10422,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1203">
+            <xdr:cNvPr hidden="1" name="A61" id="1251">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1203"/>
+                  <a14:compatExt spid="_x0000_s1251"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9072,10 +10508,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1204">
+            <xdr:cNvPr hidden="1" name="A62" id="1252">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1204"/>
+                  <a14:compatExt spid="_x0000_s1252"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9158,10 +10594,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1205">
+            <xdr:cNvPr hidden="1" name="A63" id="1253">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1205"/>
+                  <a14:compatExt spid="_x0000_s1253"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9244,10 +10680,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1206">
+            <xdr:cNvPr hidden="1" name="A64" id="1254">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1206"/>
+                  <a14:compatExt spid="_x0000_s1254"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9330,10 +10766,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1207">
+            <xdr:cNvPr hidden="1" name="A65" id="1255">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1207"/>
+                  <a14:compatExt spid="_x0000_s1255"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9416,10 +10852,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1208">
+            <xdr:cNvPr hidden="1" name="A66" id="1256">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1208"/>
+                  <a14:compatExt spid="_x0000_s1256"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9502,10 +10938,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A67" id="1209">
+            <xdr:cNvPr hidden="1" name="A67" id="1257">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1209"/>
+                  <a14:compatExt spid="_x0000_s1257"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9588,10 +11024,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A68" id="1210">
+            <xdr:cNvPr hidden="1" name="A68" id="1258">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1210"/>
+                  <a14:compatExt spid="_x0000_s1258"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9674,10 +11110,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1211">
+            <xdr:cNvPr hidden="1" name="A69" id="1259">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1211"/>
+                  <a14:compatExt spid="_x0000_s1259"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9760,10 +11196,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1212">
+            <xdr:cNvPr hidden="1" name="A70" id="1260">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1212"/>
+                  <a14:compatExt spid="_x0000_s1260"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9846,10 +11282,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A71" id="1213">
+            <xdr:cNvPr hidden="1" name="A71" id="1261">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1213"/>
+                  <a14:compatExt spid="_x0000_s1261"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9932,10 +11368,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A72" id="1214">
+            <xdr:cNvPr hidden="1" name="A72" id="1262">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1214"/>
+                  <a14:compatExt spid="_x0000_s1262"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10018,10 +11454,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A73" id="1215">
+            <xdr:cNvPr hidden="1" name="A73" id="1263">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1215"/>
+                  <a14:compatExt spid="_x0000_s1263"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10104,10 +11540,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A74" id="1216">
+            <xdr:cNvPr hidden="1" name="A74" id="1264">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1216"/>
+                  <a14:compatExt spid="_x0000_s1264"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10190,10 +11626,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A75" id="1217">
+            <xdr:cNvPr hidden="1" name="A75" id="1265">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1217"/>
+                  <a14:compatExt spid="_x0000_s1265"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10276,10 +11712,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A76" id="1218">
+            <xdr:cNvPr hidden="1" name="A76" id="1266">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1218"/>
+                  <a14:compatExt spid="_x0000_s1266"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10362,10 +11798,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A77" id="1219">
+            <xdr:cNvPr hidden="1" name="A77" id="1267">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1219"/>
+                  <a14:compatExt spid="_x0000_s1267"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10448,10 +11884,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A78" id="1220">
+            <xdr:cNvPr hidden="1" name="A78" id="1268">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1220"/>
+                  <a14:compatExt spid="_x0000_s1268"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10534,10 +11970,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A79" id="1221">
+            <xdr:cNvPr hidden="1" name="A79" id="1269">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1221"/>
+                  <a14:compatExt spid="_x0000_s1269"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10620,10 +12056,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A80" id="1222">
+            <xdr:cNvPr hidden="1" name="A80" id="1270">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1222"/>
+                  <a14:compatExt spid="_x0000_s1270"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10706,10 +12142,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A81" id="1223">
+            <xdr:cNvPr hidden="1" name="A81" id="1271">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1223"/>
+                  <a14:compatExt spid="_x0000_s1271"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10792,10 +12228,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A82" id="1224">
+            <xdr:cNvPr hidden="1" name="A82" id="1272">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1224"/>
+                  <a14:compatExt spid="_x0000_s1272"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10878,10 +12314,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A83" id="1225">
+            <xdr:cNvPr hidden="1" name="A83" id="1273">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1225"/>
+                  <a14:compatExt spid="_x0000_s1273"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10964,10 +12400,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A84" id="1226">
+            <xdr:cNvPr hidden="1" name="A84" id="1274">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1226"/>
+                  <a14:compatExt spid="_x0000_s1274"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11050,10 +12486,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A85" id="1227">
+            <xdr:cNvPr hidden="1" name="A85" id="1275">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1227"/>
+                  <a14:compatExt spid="_x0000_s1275"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11136,10 +12572,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A86" id="1228">
+            <xdr:cNvPr hidden="1" name="A86" id="1276">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1228"/>
+                  <a14:compatExt spid="_x0000_s1276"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11222,10 +12658,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A87" id="1229">
+            <xdr:cNvPr hidden="1" name="A87" id="1277">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1229"/>
+                  <a14:compatExt spid="_x0000_s1277"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11308,10 +12744,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A88" id="1230">
+            <xdr:cNvPr hidden="1" name="A88" id="1278">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1230"/>
+                  <a14:compatExt spid="_x0000_s1278"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11394,10 +12830,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A89" id="1231">
+            <xdr:cNvPr hidden="1" name="A89" id="1279">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1231"/>
+                  <a14:compatExt spid="_x0000_s1279"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11480,10 +12916,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A90" id="1232">
+            <xdr:cNvPr hidden="1" name="A90" id="1280">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1232"/>
+                  <a14:compatExt spid="_x0000_s1280"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11566,10 +13002,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A91" id="1233">
+            <xdr:cNvPr hidden="1" name="A91" id="1281">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1233"/>
+                  <a14:compatExt spid="_x0000_s1281"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11652,10 +13088,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A92" id="1234">
+            <xdr:cNvPr hidden="1" name="A92" id="1282">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1234"/>
+                  <a14:compatExt spid="_x0000_s1282"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11738,10 +13174,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A93" id="1235">
+            <xdr:cNvPr hidden="1" name="A93" id="1283">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1235"/>
+                  <a14:compatExt spid="_x0000_s1283"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11824,10 +13260,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A94" id="1236">
+            <xdr:cNvPr hidden="1" name="A94" id="1284">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1236"/>
+                  <a14:compatExt spid="_x0000_s1284"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11910,10 +13346,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A95" id="1237">
+            <xdr:cNvPr hidden="1" name="A95" id="1285">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1237"/>
+                  <a14:compatExt spid="_x0000_s1285"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11996,10 +13432,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A96" id="1238">
+            <xdr:cNvPr hidden="1" name="A96" id="1286">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1238"/>
+                  <a14:compatExt spid="_x0000_s1286"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12082,10 +13518,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A97" id="1239">
+            <xdr:cNvPr hidden="1" name="A97" id="1287">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1239"/>
+                  <a14:compatExt spid="_x0000_s1287"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12168,10 +13604,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A98" id="1240">
+            <xdr:cNvPr hidden="1" name="A98" id="1288">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1240"/>
+                  <a14:compatExt spid="_x0000_s1288"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12254,10 +13690,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A99" id="1241">
+            <xdr:cNvPr hidden="1" name="A99" id="1289">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1241"/>
+                  <a14:compatExt spid="_x0000_s1289"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12340,10 +13776,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A100" id="1242">
+            <xdr:cNvPr hidden="1" name="A100" id="1290">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1242"/>
+                  <a14:compatExt spid="_x0000_s1290"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12426,10 +13862,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A101" id="1243">
+            <xdr:cNvPr hidden="1" name="A101" id="1291">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1243"/>
+                  <a14:compatExt spid="_x0000_s1291"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12512,10 +13948,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A102" id="1244">
+            <xdr:cNvPr hidden="1" name="A102" id="1292">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1244"/>
+                  <a14:compatExt spid="_x0000_s1292"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12598,10 +14034,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A103" id="1245">
+            <xdr:cNvPr hidden="1" name="A103" id="1293">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1245"/>
+                  <a14:compatExt spid="_x0000_s1293"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12684,10 +14120,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A104" id="1246">
+            <xdr:cNvPr hidden="1" name="A104" id="1294">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1246"/>
+                  <a14:compatExt spid="_x0000_s1294"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12770,10 +14206,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A105" id="1247">
+            <xdr:cNvPr hidden="1" name="A105" id="1295">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1247"/>
+                  <a14:compatExt spid="_x0000_s1295"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12856,10 +14292,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A106" id="1248">
+            <xdr:cNvPr hidden="1" name="A106" id="1296">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1248"/>
+                  <a14:compatExt spid="_x0000_s1296"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12942,10 +14378,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A107" id="1249">
+            <xdr:cNvPr hidden="1" name="A107" id="1297">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1249"/>
+                  <a14:compatExt spid="_x0000_s1297"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13028,10 +14464,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A108" id="1250">
+            <xdr:cNvPr hidden="1" name="A108" id="1298">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1250"/>
+                  <a14:compatExt spid="_x0000_s1298"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13114,10 +14550,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A109" id="1251">
+            <xdr:cNvPr hidden="1" name="A109" id="1299">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1251"/>
+                  <a14:compatExt spid="_x0000_s1299"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13200,10 +14636,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A110" id="1252">
+            <xdr:cNvPr hidden="1" name="A110" id="1300">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1252"/>
+                  <a14:compatExt spid="_x0000_s1300"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13286,10 +14722,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A111" id="1253">
+            <xdr:cNvPr hidden="1" name="A111" id="1301">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1253"/>
+                  <a14:compatExt spid="_x0000_s1301"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13372,10 +14808,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A112" id="1254">
+            <xdr:cNvPr hidden="1" name="A112" id="1302">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1254"/>
+                  <a14:compatExt spid="_x0000_s1302"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13458,10 +14894,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A113" id="1255">
+            <xdr:cNvPr hidden="1" name="A113" id="1303">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1255"/>
+                  <a14:compatExt spid="_x0000_s1303"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13544,10 +14980,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A114" id="1256">
+            <xdr:cNvPr hidden="1" name="A114" id="1304">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1256"/>
+                  <a14:compatExt spid="_x0000_s1304"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13630,10 +15066,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A115" id="1257">
+            <xdr:cNvPr hidden="1" name="A115" id="1305">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1257"/>
+                  <a14:compatExt spid="_x0000_s1305"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13716,10 +15152,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A116" id="1258">
+            <xdr:cNvPr hidden="1" name="A116" id="1306">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1258"/>
+                  <a14:compatExt spid="_x0000_s1306"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13802,10 +15238,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A117" id="1259">
+            <xdr:cNvPr hidden="1" name="A117" id="1307">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1259"/>
+                  <a14:compatExt spid="_x0000_s1307"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13888,10 +15324,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A118" id="1260">
+            <xdr:cNvPr hidden="1" name="A118" id="1308">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1260"/>
+                  <a14:compatExt spid="_x0000_s1308"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13974,10 +15410,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A119" id="1261">
+            <xdr:cNvPr hidden="1" name="A119" id="1309">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1261"/>
+                  <a14:compatExt spid="_x0000_s1309"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14060,10 +15496,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A120" id="1262">
+            <xdr:cNvPr hidden="1" name="A120" id="1310">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1262"/>
+                  <a14:compatExt spid="_x0000_s1310"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14146,10 +15582,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A121" id="1263">
+            <xdr:cNvPr hidden="1" name="A121" id="1311">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1263"/>
+                  <a14:compatExt spid="_x0000_s1311"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14232,10 +15668,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A122" id="1264">
+            <xdr:cNvPr hidden="1" name="A122" id="1312">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1264"/>
+                  <a14:compatExt spid="_x0000_s1312"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14318,10 +15754,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A123" id="1265">
+            <xdr:cNvPr hidden="1" name="A123" id="1313">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1265"/>
+                  <a14:compatExt spid="_x0000_s1313"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14404,10 +15840,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A124" id="1266">
+            <xdr:cNvPr hidden="1" name="A124" id="1314">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1266"/>
+                  <a14:compatExt spid="_x0000_s1314"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14490,10 +15926,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A125" id="1267">
+            <xdr:cNvPr hidden="1" name="A125" id="1315">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1267"/>
+                  <a14:compatExt spid="_x0000_s1315"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14576,10 +16012,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A126" id="1268">
+            <xdr:cNvPr hidden="1" name="A126" id="1316">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1268"/>
+                  <a14:compatExt spid="_x0000_s1316"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14662,10 +16098,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A127" id="1269">
+            <xdr:cNvPr hidden="1" name="A127" id="1317">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1269"/>
+                  <a14:compatExt spid="_x0000_s1317"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14748,10 +16184,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A128" id="1270">
+            <xdr:cNvPr hidden="1" name="A128" id="1318">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1270"/>
+                  <a14:compatExt spid="_x0000_s1318"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14834,10 +16270,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A129" id="1271">
+            <xdr:cNvPr hidden="1" name="A129" id="1319">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1271"/>
+                  <a14:compatExt spid="_x0000_s1319"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14920,10 +16356,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A130" id="1272">
+            <xdr:cNvPr hidden="1" name="A130" id="1320">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1272"/>
+                  <a14:compatExt spid="_x0000_s1320"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -14989,12 +16425,3108 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>130</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>131</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A131" id="1321">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1321"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>131</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>132</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A132" id="1322">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1322"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>132</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>133</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A133" id="1323">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1323"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>133</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>134</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A134" id="1324">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1324"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>134</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>135</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A135" id="1325">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1325"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>135</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>136</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A136" id="1326">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1326"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>136</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>137</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A137" id="1327">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1327"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>137</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>138</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A138" id="1328">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1328"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>138</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>139</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A139" id="1329">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1329"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>139</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>140</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A140" id="1330">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1330"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>140</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>141</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A141" id="1331">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1331"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>141</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>142</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A142" id="1332">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1332"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>142</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>143</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A143" id="1333">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1333"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>143</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>144</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A144" id="1334">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1334"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>144</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>145</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A145" id="1335">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1335"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>145</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>146</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A146" id="1336">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1336"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>146</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>147</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A147" id="1337">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1337"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>147</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>148</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A148" id="1338">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1338"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>148</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>149</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A149" id="1339">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1339"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>149</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>150</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A150" id="1340">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1340"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>150</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>151</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A151" id="1341">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1341"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>151</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>152</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A152" id="1342">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1342"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>152</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>153</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A153" id="1343">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1343"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>153</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>154</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A154" id="1344">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1344"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>154</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>155</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A155" id="1345">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1345"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>155</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>156</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A156" id="1346">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1346"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>156</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>157</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A157" id="1347">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1347"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>157</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>158</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A158" id="1348">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1348"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>158</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>159</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A159" id="1349">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1349"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>159</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>160</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A160" id="1350">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1350"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>160</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>161</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A161" id="1351">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1351"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>161</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>162</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A162" id="1352">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1352"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>162</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>163</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A163" id="1353">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1353"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>163</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>164</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A164" id="1354">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1354"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>164</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>165</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A165" id="1355">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1355"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>165</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>166</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A166" id="1356">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1356"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -15593,58 +20125,58 @@
         <v>68</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1"/>
       <c r="B67" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1"/>
       <c r="B68" s="0" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1"/>
       <c r="B69" s="0" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1"/>
       <c r="B70" s="0" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1"/>
       <c r="B71" s="0" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1"/>
       <c r="B72" s="0" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C72" s="0" t="s">
         <v>3</v>
@@ -15653,7 +20185,7 @@
     <row r="73">
       <c r="A73" s="1"/>
       <c r="B73" s="0" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>3</v>
@@ -15662,169 +20194,169 @@
     <row r="74">
       <c r="A74" s="1"/>
       <c r="B74" s="0" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1"/>
       <c r="B75" s="0" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1"/>
       <c r="B76" s="0" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1"/>
       <c r="B77" s="0" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1"/>
       <c r="B78" s="0" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1"/>
       <c r="B79" s="0" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1"/>
       <c r="B80" s="0" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>95</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1"/>
       <c r="B81" s="0" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1"/>
       <c r="B82" s="0" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1"/>
       <c r="B83" s="0" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>101</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1"/>
       <c r="B84" s="0" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1"/>
       <c r="B85" s="0" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>105</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1"/>
       <c r="B86" s="0" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>107</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1"/>
       <c r="B87" s="0" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1"/>
       <c r="B88" s="0" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1"/>
       <c r="B89" s="0" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>113</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1"/>
       <c r="B90" s="0" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1"/>
       <c r="B91" s="0" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1"/>
       <c r="B92" s="0" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>3</v>
@@ -15833,7 +20365,7 @@
     <row r="93">
       <c r="A93" s="1"/>
       <c r="B93" s="0" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C93" s="0" t="s">
         <v>3</v>
@@ -15842,7 +20374,7 @@
     <row r="94">
       <c r="A94" s="1"/>
       <c r="B94" s="0" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>3</v>
@@ -15851,7 +20383,7 @@
     <row r="95">
       <c r="A95" s="1"/>
       <c r="B95" s="0" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C95" s="0" t="s">
         <v>3</v>
@@ -15860,7 +20392,7 @@
     <row r="96">
       <c r="A96" s="1"/>
       <c r="B96" s="0" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C96" s="0" t="s">
         <v>3</v>
@@ -15869,7 +20401,7 @@
     <row r="97">
       <c r="A97" s="1"/>
       <c r="B97" s="0" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>3</v>
@@ -15878,7 +20410,7 @@
     <row r="98">
       <c r="A98" s="1"/>
       <c r="B98" s="0" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C98" s="0" t="s">
         <v>3</v>
@@ -15887,7 +20419,7 @@
     <row r="99">
       <c r="A99" s="1"/>
       <c r="B99" s="0" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C99" s="0" t="s">
         <v>3</v>
@@ -15896,7 +20428,7 @@
     <row r="100">
       <c r="A100" s="1"/>
       <c r="B100" s="0" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C100" s="0" t="s">
         <v>3</v>
@@ -15905,7 +20437,7 @@
     <row r="101">
       <c r="A101" s="1"/>
       <c r="B101" s="0" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="C101" s="0" t="s">
         <v>3</v>
@@ -15914,61 +20446,61 @@
     <row r="102">
       <c r="A102" s="1"/>
       <c r="B102" s="0" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1"/>
       <c r="B103" s="0" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1"/>
       <c r="B104" s="0" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1"/>
       <c r="B105" s="0" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>3</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1"/>
       <c r="B106" s="0" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>3</v>
+        <v>113</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1"/>
       <c r="B107" s="0" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1"/>
       <c r="B108" s="0" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C108" s="0" t="s">
         <v>3</v>
@@ -15977,7 +20509,7 @@
     <row r="109">
       <c r="A109" s="1"/>
       <c r="B109" s="0" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C109" s="0" t="s">
         <v>3</v>
@@ -15986,154 +20518,154 @@
     <row r="110">
       <c r="A110" s="1"/>
       <c r="B110" s="0" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>3</v>
+        <v>119</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1"/>
       <c r="B111" s="0" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>3</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1"/>
       <c r="B112" s="0" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>3</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1"/>
       <c r="B113" s="0" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>3</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1"/>
       <c r="B114" s="0" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1"/>
       <c r="B115" s="0" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>3</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1"/>
       <c r="B116" s="0" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>3</v>
+        <v>131</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1"/>
       <c r="B117" s="0" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>3</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1"/>
       <c r="B118" s="0" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1"/>
       <c r="B119" s="0" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>3</v>
+        <v>137</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1"/>
       <c r="B120" s="0" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1"/>
       <c r="B121" s="0" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>3</v>
+        <v>141</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1"/>
       <c r="B122" s="0" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>3</v>
+        <v>143</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1"/>
       <c r="B123" s="0" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>3</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1"/>
       <c r="B124" s="0" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1"/>
       <c r="B125" s="0" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1"/>
       <c r="B126" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="C126" s="0" t="s">
         <v>151</v>
-      </c>
-      <c r="C126" s="0" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -16142,7 +20674,7 @@
         <v>152</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
     </row>
     <row r="128">
@@ -16151,24 +20683,348 @@
         <v>153</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>154</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1"/>
       <c r="B129" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>156</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1"/>
       <c r="B130" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="C130" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1"/>
+      <c r="B131" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1"/>
+      <c r="B132" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="C130" s="0" t="s">
+      <c r="C132" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1"/>
+      <c r="B133" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="C133" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1"/>
+      <c r="B134" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="C134" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1"/>
+      <c r="B135" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="C135" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1"/>
+      <c r="B136" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="C136" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1"/>
+      <c r="B137" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C137" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1"/>
+      <c r="B138" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C138" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1"/>
+      <c r="B139" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1"/>
+      <c r="B140" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="C140" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1"/>
+      <c r="B141" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1"/>
+      <c r="B142" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1"/>
+      <c r="B143" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C143" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1"/>
+      <c r="B144" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C144" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1"/>
+      <c r="B145" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C145" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1"/>
+      <c r="B146" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C146" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1"/>
+      <c r="B147" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="C147" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1"/>
+      <c r="B148" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="C148" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1"/>
+      <c r="B149" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C149" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1"/>
+      <c r="B150" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="C150" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1"/>
+      <c r="B151" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C151" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1"/>
+      <c r="B152" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C152" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1"/>
+      <c r="B153" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1"/>
+      <c r="B154" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1"/>
+      <c r="B155" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1"/>
+      <c r="B156" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="C156" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1"/>
+      <c r="B157" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C157" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1"/>
+      <c r="B158" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="C158" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1"/>
+      <c r="B159" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C159" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1"/>
+      <c r="B160" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="C160" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1"/>
+      <c r="B161" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="C161" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1"/>
+      <c r="B162" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="C162" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1"/>
+      <c r="B163" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C163" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1"/>
+      <c r="B164" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1"/>
+      <c r="B165" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="C165" s="0" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1"/>
+      <c r="B166" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C166" s="0" t="s">
         <v>3</v>
       </c>
     </row>
@@ -16181,7 +21037,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId659" name="A1">
+            <control shapeId="1191" r:id="rId953" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16203,7 +21059,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId660" name="A2">
+            <control shapeId="1192" r:id="rId954" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16225,7 +21081,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId661" name="A3">
+            <control shapeId="1193" r:id="rId955" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16247,7 +21103,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId662" name="A4">
+            <control shapeId="1194" r:id="rId956" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16269,7 +21125,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId663" name="A5">
+            <control shapeId="1195" r:id="rId957" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16291,7 +21147,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId664" name="A6">
+            <control shapeId="1196" r:id="rId958" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16313,7 +21169,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId665" name="A7">
+            <control shapeId="1197" r:id="rId959" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16335,7 +21191,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId666" name="A8">
+            <control shapeId="1198" r:id="rId960" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16357,7 +21213,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId667" name="A9">
+            <control shapeId="1199" r:id="rId961" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16379,7 +21235,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId668" name="A10">
+            <control shapeId="1200" r:id="rId962" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16401,7 +21257,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId669" name="A11">
+            <control shapeId="1201" r:id="rId963" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16423,7 +21279,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId670" name="A12">
+            <control shapeId="1202" r:id="rId964" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16445,7 +21301,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId671" name="A13">
+            <control shapeId="1203" r:id="rId965" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16467,7 +21323,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId672" name="A14">
+            <control shapeId="1204" r:id="rId966" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16489,7 +21345,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId673" name="A15">
+            <control shapeId="1205" r:id="rId967" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16511,7 +21367,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1158" r:id="rId674" name="A16">
+            <control shapeId="1206" r:id="rId968" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16533,7 +21389,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1159" r:id="rId675" name="A17">
+            <control shapeId="1207" r:id="rId969" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16555,7 +21411,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1160" r:id="rId676" name="A18">
+            <control shapeId="1208" r:id="rId970" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16577,7 +21433,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1161" r:id="rId677" name="A19">
+            <control shapeId="1209" r:id="rId971" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16599,7 +21455,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1162" r:id="rId678" name="A20">
+            <control shapeId="1210" r:id="rId972" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16621,7 +21477,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1163" r:id="rId679" name="A21">
+            <control shapeId="1211" r:id="rId973" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16643,7 +21499,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId680" name="A22">
+            <control shapeId="1212" r:id="rId974" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16665,7 +21521,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1165" r:id="rId681" name="A23">
+            <control shapeId="1213" r:id="rId975" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16687,7 +21543,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1166" r:id="rId682" name="A24">
+            <control shapeId="1214" r:id="rId976" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16709,7 +21565,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1167" r:id="rId683" name="A25">
+            <control shapeId="1215" r:id="rId977" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16731,7 +21587,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1168" r:id="rId684" name="A26">
+            <control shapeId="1216" r:id="rId978" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16753,7 +21609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1169" r:id="rId685" name="A27">
+            <control shapeId="1217" r:id="rId979" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16775,7 +21631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1170" r:id="rId686" name="A28">
+            <control shapeId="1218" r:id="rId980" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16797,7 +21653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1171" r:id="rId687" name="A29">
+            <control shapeId="1219" r:id="rId981" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16819,7 +21675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1172" r:id="rId688" name="A30">
+            <control shapeId="1220" r:id="rId982" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16841,7 +21697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1173" r:id="rId689" name="A31">
+            <control shapeId="1221" r:id="rId983" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16863,7 +21719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1174" r:id="rId690" name="A32">
+            <control shapeId="1222" r:id="rId984" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16885,7 +21741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1175" r:id="rId691" name="A33">
+            <control shapeId="1223" r:id="rId985" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16907,7 +21763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1176" r:id="rId692" name="A34">
+            <control shapeId="1224" r:id="rId986" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16929,7 +21785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1177" r:id="rId693" name="A35">
+            <control shapeId="1225" r:id="rId987" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16951,7 +21807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1178" r:id="rId694" name="A36">
+            <control shapeId="1226" r:id="rId988" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16973,7 +21829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1179" r:id="rId695" name="A37">
+            <control shapeId="1227" r:id="rId989" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16995,7 +21851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1180" r:id="rId696" name="A38">
+            <control shapeId="1228" r:id="rId990" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17017,7 +21873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1181" r:id="rId697" name="A39">
+            <control shapeId="1229" r:id="rId991" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17039,7 +21895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1182" r:id="rId698" name="A40">
+            <control shapeId="1230" r:id="rId992" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17061,7 +21917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1183" r:id="rId699" name="A41">
+            <control shapeId="1231" r:id="rId993" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17083,7 +21939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1184" r:id="rId700" name="A42">
+            <control shapeId="1232" r:id="rId994" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17105,7 +21961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1185" r:id="rId701" name="A43">
+            <control shapeId="1233" r:id="rId995" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17127,7 +21983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1186" r:id="rId702" name="A44">
+            <control shapeId="1234" r:id="rId996" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17149,7 +22005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1187" r:id="rId703" name="A45">
+            <control shapeId="1235" r:id="rId997" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17171,7 +22027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1188" r:id="rId704" name="A46">
+            <control shapeId="1236" r:id="rId998" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17193,7 +22049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1189" r:id="rId705" name="A47">
+            <control shapeId="1237" r:id="rId999" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17215,7 +22071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1190" r:id="rId706" name="A48">
+            <control shapeId="1238" r:id="rId1000" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17237,7 +22093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1191" r:id="rId707" name="A49">
+            <control shapeId="1239" r:id="rId1001" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17259,7 +22115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1192" r:id="rId708" name="A50">
+            <control shapeId="1240" r:id="rId1002" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17281,7 +22137,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1193" r:id="rId709" name="A51">
+            <control shapeId="1241" r:id="rId1003" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17303,7 +22159,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1194" r:id="rId710" name="A52">
+            <control shapeId="1242" r:id="rId1004" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17325,7 +22181,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1195" r:id="rId711" name="A53">
+            <control shapeId="1243" r:id="rId1005" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17347,7 +22203,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1196" r:id="rId712" name="A54">
+            <control shapeId="1244" r:id="rId1006" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17369,7 +22225,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1197" r:id="rId713" name="A55">
+            <control shapeId="1245" r:id="rId1007" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17391,7 +22247,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1198" r:id="rId714" name="A56">
+            <control shapeId="1246" r:id="rId1008" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17413,7 +22269,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1199" r:id="rId715" name="A57">
+            <control shapeId="1247" r:id="rId1009" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17435,7 +22291,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1200" r:id="rId716" name="A58">
+            <control shapeId="1248" r:id="rId1010" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17457,7 +22313,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1201" r:id="rId717" name="A59">
+            <control shapeId="1249" r:id="rId1011" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17479,7 +22335,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1202" r:id="rId718" name="A60">
+            <control shapeId="1250" r:id="rId1012" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17501,7 +22357,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1203" r:id="rId719" name="A61">
+            <control shapeId="1251" r:id="rId1013" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17523,7 +22379,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1204" r:id="rId720" name="A62">
+            <control shapeId="1252" r:id="rId1014" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17545,7 +22401,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1205" r:id="rId721" name="A63">
+            <control shapeId="1253" r:id="rId1015" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17567,7 +22423,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1206" r:id="rId722" name="A64">
+            <control shapeId="1254" r:id="rId1016" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17589,7 +22445,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1207" r:id="rId723" name="A65">
+            <control shapeId="1255" r:id="rId1017" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17611,7 +22467,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1208" r:id="rId724" name="A66">
+            <control shapeId="1256" r:id="rId1018" name="A66">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17633,7 +22489,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1209" r:id="rId725" name="A67">
+            <control shapeId="1257" r:id="rId1019" name="A67">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17655,7 +22511,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1210" r:id="rId726" name="A68">
+            <control shapeId="1258" r:id="rId1020" name="A68">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17677,7 +22533,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1211" r:id="rId727" name="A69">
+            <control shapeId="1259" r:id="rId1021" name="A69">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17699,7 +22555,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1212" r:id="rId728" name="A70">
+            <control shapeId="1260" r:id="rId1022" name="A70">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17721,7 +22577,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1213" r:id="rId729" name="A71">
+            <control shapeId="1261" r:id="rId1023" name="A71">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17743,7 +22599,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1214" r:id="rId730" name="A72">
+            <control shapeId="1262" r:id="rId1024" name="A72">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17765,7 +22621,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1215" r:id="rId731" name="A73">
+            <control shapeId="1263" r:id="rId1025" name="A73">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17787,7 +22643,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1216" r:id="rId732" name="A74">
+            <control shapeId="1264" r:id="rId1026" name="A74">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17809,7 +22665,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1217" r:id="rId733" name="A75">
+            <control shapeId="1265" r:id="rId1027" name="A75">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17831,7 +22687,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1218" r:id="rId734" name="A76">
+            <control shapeId="1266" r:id="rId1028" name="A76">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17853,7 +22709,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1219" r:id="rId735" name="A77">
+            <control shapeId="1267" r:id="rId1029" name="A77">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17875,7 +22731,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1220" r:id="rId736" name="A78">
+            <control shapeId="1268" r:id="rId1030" name="A78">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17897,7 +22753,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1221" r:id="rId737" name="A79">
+            <control shapeId="1269" r:id="rId1031" name="A79">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17919,7 +22775,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1222" r:id="rId738" name="A80">
+            <control shapeId="1270" r:id="rId1032" name="A80">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17941,7 +22797,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1223" r:id="rId739" name="A81">
+            <control shapeId="1271" r:id="rId1033" name="A81">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17963,7 +22819,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1224" r:id="rId740" name="A82">
+            <control shapeId="1272" r:id="rId1034" name="A82">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17985,7 +22841,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1225" r:id="rId741" name="A83">
+            <control shapeId="1273" r:id="rId1035" name="A83">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18007,7 +22863,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1226" r:id="rId742" name="A84">
+            <control shapeId="1274" r:id="rId1036" name="A84">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18029,7 +22885,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1227" r:id="rId743" name="A85">
+            <control shapeId="1275" r:id="rId1037" name="A85">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18051,7 +22907,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1228" r:id="rId744" name="A86">
+            <control shapeId="1276" r:id="rId1038" name="A86">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18073,7 +22929,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1229" r:id="rId745" name="A87">
+            <control shapeId="1277" r:id="rId1039" name="A87">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18095,7 +22951,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1230" r:id="rId746" name="A88">
+            <control shapeId="1278" r:id="rId1040" name="A88">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18117,7 +22973,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1231" r:id="rId747" name="A89">
+            <control shapeId="1279" r:id="rId1041" name="A89">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18139,7 +22995,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1232" r:id="rId748" name="A90">
+            <control shapeId="1280" r:id="rId1042" name="A90">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18161,7 +23017,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1233" r:id="rId749" name="A91">
+            <control shapeId="1281" r:id="rId1043" name="A91">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18183,7 +23039,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1234" r:id="rId750" name="A92">
+            <control shapeId="1282" r:id="rId1044" name="A92">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18205,7 +23061,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1235" r:id="rId751" name="A93">
+            <control shapeId="1283" r:id="rId1045" name="A93">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18227,7 +23083,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1236" r:id="rId752" name="A94">
+            <control shapeId="1284" r:id="rId1046" name="A94">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18249,7 +23105,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1237" r:id="rId753" name="A95">
+            <control shapeId="1285" r:id="rId1047" name="A95">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18271,7 +23127,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1238" r:id="rId754" name="A96">
+            <control shapeId="1286" r:id="rId1048" name="A96">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18293,7 +23149,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1239" r:id="rId755" name="A97">
+            <control shapeId="1287" r:id="rId1049" name="A97">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18315,7 +23171,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1240" r:id="rId756" name="A98">
+            <control shapeId="1288" r:id="rId1050" name="A98">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18337,7 +23193,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1241" r:id="rId757" name="A99">
+            <control shapeId="1289" r:id="rId1051" name="A99">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18359,7 +23215,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1242" r:id="rId758" name="A100">
+            <control shapeId="1290" r:id="rId1052" name="A100">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18381,7 +23237,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1243" r:id="rId759" name="A101">
+            <control shapeId="1291" r:id="rId1053" name="A101">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18403,7 +23259,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1244" r:id="rId760" name="A102">
+            <control shapeId="1292" r:id="rId1054" name="A102">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18425,7 +23281,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1245" r:id="rId761" name="A103">
+            <control shapeId="1293" r:id="rId1055" name="A103">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18447,7 +23303,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1246" r:id="rId762" name="A104">
+            <control shapeId="1294" r:id="rId1056" name="A104">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18469,7 +23325,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1247" r:id="rId763" name="A105">
+            <control shapeId="1295" r:id="rId1057" name="A105">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18491,7 +23347,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1248" r:id="rId764" name="A106">
+            <control shapeId="1296" r:id="rId1058" name="A106">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18513,7 +23369,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1249" r:id="rId765" name="A107">
+            <control shapeId="1297" r:id="rId1059" name="A107">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18535,7 +23391,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1250" r:id="rId766" name="A108">
+            <control shapeId="1298" r:id="rId1060" name="A108">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18557,7 +23413,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1251" r:id="rId767" name="A109">
+            <control shapeId="1299" r:id="rId1061" name="A109">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18579,7 +23435,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1252" r:id="rId768" name="A110">
+            <control shapeId="1300" r:id="rId1062" name="A110">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18601,7 +23457,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1253" r:id="rId769" name="A111">
+            <control shapeId="1301" r:id="rId1063" name="A111">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18623,7 +23479,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1254" r:id="rId770" name="A112">
+            <control shapeId="1302" r:id="rId1064" name="A112">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18645,7 +23501,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1255" r:id="rId771" name="A113">
+            <control shapeId="1303" r:id="rId1065" name="A113">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18667,7 +23523,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1256" r:id="rId772" name="A114">
+            <control shapeId="1304" r:id="rId1066" name="A114">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18689,7 +23545,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1257" r:id="rId773" name="A115">
+            <control shapeId="1305" r:id="rId1067" name="A115">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18711,7 +23567,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1258" r:id="rId774" name="A116">
+            <control shapeId="1306" r:id="rId1068" name="A116">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18733,7 +23589,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1259" r:id="rId775" name="A117">
+            <control shapeId="1307" r:id="rId1069" name="A117">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18755,7 +23611,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1260" r:id="rId776" name="A118">
+            <control shapeId="1308" r:id="rId1070" name="A118">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18777,7 +23633,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1261" r:id="rId777" name="A119">
+            <control shapeId="1309" r:id="rId1071" name="A119">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18799,7 +23655,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1262" r:id="rId778" name="A120">
+            <control shapeId="1310" r:id="rId1072" name="A120">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18821,7 +23677,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1263" r:id="rId779" name="A121">
+            <control shapeId="1311" r:id="rId1073" name="A121">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18843,7 +23699,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1264" r:id="rId780" name="A122">
+            <control shapeId="1312" r:id="rId1074" name="A122">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18865,7 +23721,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1265" r:id="rId781" name="A123">
+            <control shapeId="1313" r:id="rId1075" name="A123">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18887,7 +23743,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1266" r:id="rId782" name="A124">
+            <control shapeId="1314" r:id="rId1076" name="A124">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18909,7 +23765,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1267" r:id="rId783" name="A125">
+            <control shapeId="1315" r:id="rId1077" name="A125">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18931,7 +23787,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1268" r:id="rId784" name="A126">
+            <control shapeId="1316" r:id="rId1078" name="A126">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18953,7 +23809,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1269" r:id="rId785" name="A127">
+            <control shapeId="1317" r:id="rId1079" name="A127">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18975,7 +23831,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1270" r:id="rId786" name="A128">
+            <control shapeId="1318" r:id="rId1080" name="A128">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -18997,7 +23853,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1271" r:id="rId787" name="A129">
+            <control shapeId="1319" r:id="rId1081" name="A129">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -19019,7 +23875,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1272" r:id="rId788" name="A130">
+            <control shapeId="1320" r:id="rId1082" name="A130">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -19032,6 +23888,798 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>130</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1321" r:id="rId1083" name="A131">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>130</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>131</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1322" r:id="rId1084" name="A132">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>131</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>132</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1323" r:id="rId1085" name="A133">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>132</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>133</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1324" r:id="rId1086" name="A134">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>133</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>134</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1325" r:id="rId1087" name="A135">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>134</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>135</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1326" r:id="rId1088" name="A136">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>135</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>136</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1327" r:id="rId1089" name="A137">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>136</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>137</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1328" r:id="rId1090" name="A138">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>137</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>138</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1329" r:id="rId1091" name="A139">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>138</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>139</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1330" r:id="rId1092" name="A140">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>139</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>140</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1331" r:id="rId1093" name="A141">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>140</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>141</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1332" r:id="rId1094" name="A142">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>141</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>142</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1333" r:id="rId1095" name="A143">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>142</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>143</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1334" r:id="rId1096" name="A144">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>143</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>144</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1335" r:id="rId1097" name="A145">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>144</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>145</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1336" r:id="rId1098" name="A146">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>145</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>146</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1337" r:id="rId1099" name="A147">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>146</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>147</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1338" r:id="rId1100" name="A148">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>147</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>148</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1339" r:id="rId1101" name="A149">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>148</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>149</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1340" r:id="rId1102" name="A150">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>149</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>150</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1341" r:id="rId1103" name="A151">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>150</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>151</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1342" r:id="rId1104" name="A152">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>151</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>152</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1343" r:id="rId1105" name="A153">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>152</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>153</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1344" r:id="rId1106" name="A154">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>153</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>154</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1345" r:id="rId1107" name="A155">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>154</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>155</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1346" r:id="rId1108" name="A156">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>155</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>156</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1347" r:id="rId1109" name="A157">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>156</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>157</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1348" r:id="rId1110" name="A158">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>157</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>158</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1349" r:id="rId1111" name="A159">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>158</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>159</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1350" r:id="rId1112" name="A160">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>159</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>160</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1351" r:id="rId1113" name="A161">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>160</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>161</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1352" r:id="rId1114" name="A162">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>161</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>162</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1353" r:id="rId1115" name="A163">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>162</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>163</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1354" r:id="rId1116" name="A164">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>163</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>164</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1355" r:id="rId1117" name="A165">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>164</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>165</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1356" r:id="rId1118" name="A166">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>165</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>166</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
   <si>
     <t>Archetype.Butchery</t>
   </si>
@@ -3379,6 +3379,132 @@
   </si>
   <si>
     <t>실험용 지형에서 도전합니다.</t>
+  </si>
+  <si>
+    <t>Story.Speaker.Director</t>
+  </si>
+  <si>
+    <t>Story.Speaker.Broker</t>
+  </si>
+  <si>
+    <t>LvEnter.Comm.Title</t>
+  </si>
+  <si>
+    <t>LvEnter.Objective.Title</t>
+  </si>
+  <si>
+    <t>LvEnter.Tag.Title</t>
+  </si>
+  <si>
+    <t>LvEnter.HistoryOffset</t>
+  </si>
+  <si>
+    <t>LvEnter.CurrentOffset</t>
+  </si>
+  <si>
+    <t>LvEnter.Grade</t>
+  </si>
+  <si>
+    <t>LvEnter.Badge.Plain</t>
+  </si>
+  <si>
+    <t>LvEnter.Badge.Bronze</t>
+  </si>
+  <si>
+    <t>LvEnter.Badge.Silver</t>
+  </si>
+  <si>
+    <t>LvEnter.Badge.Gold</t>
+  </si>
+  <si>
+    <t>LvEnter.Badge.Diamond</t>
+  </si>
+  <si>
+    <t>LvEnter.Signal.Normal</t>
+  </si>
+  <si>
+    <t>LvEnter.Signal.Corrupted</t>
+  </si>
+  <si>
+    <t>LvEnter.Signal.Weak</t>
+  </si>
+  <si>
+    <t>LvEnter.Signal.Fragment</t>
+  </si>
+  <si>
+    <t>LvEnter.Replay</t>
+  </si>
+  <si>
+    <t>LvEnter.Collapse</t>
+  </si>
+  <si>
+    <t>LvEnter.Expand</t>
+  </si>
+  <si>
+    <t>Story.Comm.L1.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L1.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L2.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L2.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L3.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L3.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L4.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L4.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L5.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L5.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L6.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L6.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L7.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L7.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L8.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L8.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L9.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L9.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L10.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.L10.Secondary</t>
+  </si>
+  <si>
+    <t>Story.Comm.LTest.Primary</t>
+  </si>
+  <si>
+    <t>Story.Comm.LTest.Secondary</t>
   </si>
 </sst>
 </file>
@@ -3834,12 +3960,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1012"/>
+  <dimension ref="A1:C1054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
@@ -10158,6 +10284,216 @@
         <v>1121</v>
       </c>
     </row>
+    <row r="1013">
+      <c r="B1013" s="0" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="B1014" s="0" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="B1015" s="0" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="B1016" s="0" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="B1017" s="0" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="B1018" s="0" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="B1019" s="0" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="B1020" s="0" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="B1021" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="B1022" s="0" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="B1023" s="0" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="B1024" s="0" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="B1025" s="0" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="B1026" s="0" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="B1027" s="0" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="B1028" s="0" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="B1029" s="0" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="B1030" s="0" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="B1031" s="0" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="B1032" s="0" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="B1033" s="0" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="B1034" s="0" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="B1035" s="0" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="B1036" s="0" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="B1037" s="0" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="B1038" s="0" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="B1039" s="0" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="B1040" s="0" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="B1041" s="0" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="B1042" s="0" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="B1043" s="0" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="B1044" s="0" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="B1045" s="0" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="B1046" s="0" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="B1047" s="0" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="B1048" s="0" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="B1049" s="0" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="B1050" s="0" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="B1051" s="0" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="B1052" s="0" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="B1053" s="0" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="B1054" s="0" t="s">
+        <v>1163</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="1172">
   <si>
     <t>Archetype.Butchery</t>
   </si>
@@ -3405,19 +3405,22 @@
     <t>LvEnter.Grade</t>
   </si>
   <si>
-    <t>LvEnter.Badge.Plain</t>
-  </si>
-  <si>
-    <t>LvEnter.Badge.Bronze</t>
-  </si>
-  <si>
-    <t>LvEnter.Badge.Silver</t>
-  </si>
-  <si>
-    <t>LvEnter.Badge.Gold</t>
-  </si>
-  <si>
-    <t>LvEnter.Badge.Diamond</t>
+    <t/>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Button</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Title</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.ClearedLevels</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.ClearedExperiments</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.UnlockedKeepsakes</t>
   </si>
   <si>
     <t>LvEnter.Signal.Normal</t>
@@ -3505,6 +3508,27 @@
   </si>
   <si>
     <t>Story.Comm.LTest.Secondary</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.GrowthPoints</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.BadgeThresholds</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.MaxOffset</t>
+  </si>
+  <si>
+    <t>LvEnter.CareerRecord.Close</t>
+  </si>
+  <si>
+    <t>CareerSettlement.ExperienceGrade</t>
+  </si>
+  <si>
+    <t>CareerSettlement.ExperienceBreakdown</t>
+  </si>
+  <si>
+    <t>CareerSettlement.OffsetMultiplier</t>
   </si>
 </sst>
 </file>
@@ -3965,7 +3989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1054"/>
+  <dimension ref="A1:C1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
@@ -10323,175 +10347,249 @@
       <c r="B1020" s="0" t="s">
         <v>1129</v>
       </c>
+      <c r="C1020" s="0" t="s">
+        <v>1130</v>
+      </c>
     </row>
     <row r="1021">
       <c r="B1021" s="0" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1021" s="0" t="s">
         <v>1130</v>
       </c>
     </row>
     <row r="1022">
       <c r="B1022" s="0" t="s">
-        <v>1131</v>
+        <v>1132</v>
+      </c>
+      <c r="C1022" s="0" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="1023">
       <c r="B1023" s="0" t="s">
-        <v>1132</v>
+        <v>1133</v>
+      </c>
+      <c r="C1023" s="0" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="1024">
       <c r="B1024" s="0" t="s">
-        <v>1133</v>
+        <v>1134</v>
+      </c>
+      <c r="C1024" s="0" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="1025">
       <c r="B1025" s="0" t="s">
-        <v>1134</v>
+        <v>1135</v>
+      </c>
+      <c r="C1025" s="0" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="1026">
       <c r="B1026" s="0" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1027">
       <c r="B1027" s="0" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1028">
       <c r="B1028" s="0" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1029">
       <c r="B1029" s="0" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1030">
       <c r="B1030" s="0" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1031">
       <c r="B1031" s="0" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1032">
       <c r="B1032" s="0" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1033">
       <c r="B1033" s="0" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1034">
       <c r="B1034" s="0" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1035">
       <c r="B1035" s="0" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1036">
       <c r="B1036" s="0" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1037">
       <c r="B1037" s="0" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1038">
       <c r="B1038" s="0" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1039">
       <c r="B1039" s="0" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1040">
       <c r="B1040" s="0" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1041">
       <c r="B1041" s="0" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1042">
       <c r="B1042" s="0" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1043">
       <c r="B1043" s="0" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1044">
       <c r="B1044" s="0" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1045">
       <c r="B1045" s="0" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1046">
       <c r="B1046" s="0" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1047">
       <c r="B1047" s="0" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="1048">
       <c r="B1048" s="0" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="1049">
       <c r="B1049" s="0" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="1050">
       <c r="B1050" s="0" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="1051">
       <c r="B1051" s="0" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1052">
       <c r="B1052" s="0" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="1053">
       <c r="B1053" s="0" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="1054">
       <c r="B1054" s="0" t="s">
-        <v>1163</v>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="B1055" s="0" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C1055" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="B1056" s="0" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C1056" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="B1057" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C1057" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="B1058" s="0" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C1058" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="B1059" s="0" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C1059" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="B1060" s="0" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C1060" s="0" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="B1061" s="0" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C1061" s="0" t="s">
+        <v>1130</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="1164">
   <si>
     <t>Archetype.Butchery</t>
   </si>
@@ -714,9 +714,6 @@
     <t>LvTag_Desc_BlockingTechnique</t>
   </si>
   <si>
-    <t>LvTag_Desc_CommunicationLoss</t>
-  </si>
-  <si>
     <t>LvTag_Desc_Conductor</t>
   </si>
   <si>
@@ -753,12 +750,6 @@
     <t>LvTag_Desc_Desperado</t>
   </si>
   <si>
-    <t>LvTag_Desc_DiscountedRecyclingI</t>
-  </si>
-  <si>
-    <t>LvTag_Desc_DiscountedRecyclingII</t>
-  </si>
-  <si>
     <t>LvTag_Desc_DulledSensesI</t>
   </si>
   <si>
@@ -933,9 +924,6 @@
     <t>LvTag_Desc_RuthlessMindIII</t>
   </si>
   <si>
-    <t>LvTag_Desc_ScrapRecycling</t>
-  </si>
-  <si>
     <t>LvTag_Desc_ShoddyConstructionI</t>
   </si>
   <si>
@@ -1029,9 +1017,6 @@
     <t>LvTag_Name_BlockingTechnique</t>
   </si>
   <si>
-    <t>LvTag_Name_CommunicationLoss</t>
-  </si>
-  <si>
     <t>LvTag_Name_Conductor</t>
   </si>
   <si>
@@ -1068,12 +1053,6 @@
     <t>LvTag_Name_Desperado</t>
   </si>
   <si>
-    <t>LvTag_Name_DiscountedRecyclingI</t>
-  </si>
-  <si>
-    <t>LvTag_Name_DiscountedRecyclingII</t>
-  </si>
-  <si>
     <t>LvTag_Name_DulledSensesI</t>
   </si>
   <si>
@@ -1246,9 +1225,6 @@
   </si>
   <si>
     <t>LvTag_Name_RuthlessMindIII</t>
-  </si>
-  <si>
-    <t>LvTag_Name_ScrapRecycling</t>
   </si>
   <si>
     <t>LvTag_Name_ShoddyConstructionI</t>
@@ -5391,3878 +5367,3854 @@
     </row>
     <row r="232">
       <c r="A232" s="1"/>
-      <c r="B232" s="0" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
       <c r="B233" s="0" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
       <c r="B234" s="0" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
       <c r="B235" s="0" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
       <c r="B236" s="0" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
       <c r="B237" s="0" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
       <c r="B238" s="0" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
       <c r="B239" s="0" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
       <c r="B240" s="0" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
       <c r="B241" s="0" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
       <c r="B242" s="0" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
       <c r="B243" s="0" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
       <c r="B244" s="0" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
-      <c r="B245" s="0" t="s">
-        <v>246</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
-      <c r="B246" s="0" t="s">
-        <v>247</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
       <c r="B247" s="0" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
       <c r="B248" s="0" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
       <c r="B249" s="0" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
       <c r="B250" s="0" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
       <c r="B251" s="0" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
       <c r="B252" s="0" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
       <c r="B253" s="0" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
       <c r="B254" s="0" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
       <c r="B255" s="0" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
       <c r="B256" s="0" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
       <c r="B257" s="0" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
       <c r="B258" s="0" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
       <c r="B259" s="0" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1"/>
       <c r="B260" s="0" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1"/>
       <c r="B261" s="0" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1"/>
       <c r="B262" s="0" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1"/>
       <c r="B263" s="0" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1"/>
       <c r="B264" s="0" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1"/>
       <c r="B265" s="0" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1"/>
       <c r="B266" s="0" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1"/>
       <c r="B267" s="0" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1"/>
       <c r="B268" s="0" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1"/>
       <c r="B269" s="0" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1"/>
       <c r="B270" s="0" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1"/>
       <c r="B271" s="0" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1"/>
       <c r="B272" s="0" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1"/>
       <c r="B273" s="0" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1"/>
       <c r="B274" s="0" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1"/>
       <c r="B275" s="0" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1"/>
       <c r="B276" s="0" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1"/>
       <c r="B277" s="0" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1"/>
       <c r="B278" s="0" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1"/>
       <c r="B279" s="0" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1"/>
       <c r="B280" s="0" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1"/>
       <c r="B281" s="0" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1"/>
       <c r="B282" s="0" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1"/>
       <c r="B283" s="0" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1"/>
       <c r="B284" s="0" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1"/>
       <c r="B285" s="0" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1"/>
       <c r="B286" s="0" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1"/>
       <c r="B287" s="0" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1"/>
       <c r="B288" s="0" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1"/>
       <c r="B289" s="0" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1"/>
       <c r="B290" s="0" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1"/>
       <c r="B291" s="0" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1"/>
       <c r="B292" s="0" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1"/>
       <c r="B293" s="0" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1"/>
       <c r="B294" s="0" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1"/>
       <c r="B295" s="0" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1"/>
       <c r="B296" s="0" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1"/>
       <c r="B297" s="0" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1"/>
       <c r="B298" s="0" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1"/>
       <c r="B299" s="0" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1"/>
       <c r="B300" s="0" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1"/>
       <c r="B301" s="0" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1"/>
       <c r="B302" s="0" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1"/>
       <c r="B303" s="0" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1"/>
       <c r="B304" s="0" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1"/>
-      <c r="B305" s="0" t="s">
-        <v>306</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" s="1"/>
       <c r="B306" s="0" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1"/>
       <c r="B307" s="0" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1"/>
       <c r="B308" s="0" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1"/>
       <c r="B309" s="0" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1"/>
       <c r="B310" s="0" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1"/>
       <c r="B311" s="0" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1"/>
       <c r="B312" s="0" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1"/>
       <c r="B313" s="0" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1"/>
       <c r="B314" s="0" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1"/>
       <c r="B315" s="0" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1"/>
       <c r="B316" s="0" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1"/>
       <c r="B317" s="0" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1"/>
       <c r="B318" s="0" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1"/>
       <c r="B319" s="0" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1"/>
       <c r="B320" s="0" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1"/>
       <c r="B321" s="0" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1"/>
       <c r="B322" s="0" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1"/>
       <c r="B323" s="0" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1"/>
       <c r="B324" s="0" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1"/>
       <c r="B325" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1"/>
       <c r="B326" s="0" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1"/>
       <c r="B327" s="0" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1"/>
       <c r="B328" s="0" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1"/>
       <c r="B329" s="0" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1"/>
       <c r="B330" s="0" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1"/>
       <c r="B331" s="0" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1"/>
       <c r="B332" s="0" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1"/>
       <c r="B333" s="0" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1"/>
       <c r="B334" s="0" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1"/>
       <c r="B335" s="0" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1"/>
       <c r="B336" s="0" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1"/>
-      <c r="B337" s="0" t="s">
-        <v>338</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" s="1"/>
       <c r="B338" s="0" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1"/>
       <c r="B339" s="0" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1"/>
       <c r="B340" s="0" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1"/>
       <c r="B341" s="0" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1"/>
       <c r="B342" s="0" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1"/>
       <c r="B343" s="0" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1"/>
       <c r="B344" s="0" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1"/>
       <c r="B345" s="0" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1"/>
       <c r="B346" s="0" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1"/>
       <c r="B347" s="0" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1"/>
       <c r="B348" s="0" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1"/>
       <c r="B349" s="0" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1"/>
-      <c r="B350" s="0" t="s">
-        <v>351</v>
-      </c>
     </row>
     <row r="351">
       <c r="A351" s="1"/>
-      <c r="B351" s="0" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" s="1"/>
       <c r="B352" s="0" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1"/>
       <c r="B353" s="0" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1"/>
       <c r="B354" s="0" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1"/>
       <c r="B355" s="0" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1"/>
       <c r="B356" s="0" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1"/>
       <c r="B357" s="0" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1"/>
       <c r="B358" s="0" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1"/>
       <c r="B359" s="0" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1"/>
       <c r="B360" s="0" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1"/>
       <c r="B361" s="0" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1"/>
       <c r="B362" s="0" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1"/>
       <c r="B363" s="0" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1"/>
       <c r="B364" s="0" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1"/>
       <c r="B365" s="0" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1"/>
       <c r="B366" s="0" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1"/>
       <c r="B367" s="0" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1"/>
       <c r="B368" s="0" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1"/>
       <c r="B369" s="0" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1"/>
       <c r="B370" s="0" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1"/>
       <c r="B371" s="0" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1"/>
       <c r="B372" s="0" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1"/>
       <c r="B373" s="0" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1"/>
       <c r="B374" s="0" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1"/>
       <c r="B375" s="0" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1"/>
       <c r="B376" s="0" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1"/>
       <c r="B377" s="0" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1"/>
       <c r="B378" s="0" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1"/>
       <c r="B379" s="0" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1"/>
       <c r="B380" s="0" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1"/>
       <c r="B381" s="0" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1"/>
       <c r="B382" s="0" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1"/>
       <c r="B383" s="0" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1"/>
       <c r="B384" s="0" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1"/>
       <c r="B385" s="0" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1"/>
       <c r="B386" s="0" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1"/>
       <c r="B387" s="0" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1"/>
       <c r="B388" s="0" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1"/>
       <c r="B389" s="0" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1"/>
       <c r="B390" s="0" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1"/>
       <c r="B391" s="0" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1"/>
       <c r="B392" s="0" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1"/>
       <c r="B393" s="0" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1"/>
       <c r="B394" s="0" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1"/>
       <c r="B395" s="0" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1"/>
       <c r="B396" s="0" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1"/>
       <c r="B397" s="0" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1"/>
       <c r="B398" s="0" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1"/>
       <c r="B399" s="0" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1"/>
       <c r="B400" s="0" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1"/>
       <c r="B401" s="0" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1"/>
       <c r="B402" s="0" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1"/>
       <c r="B403" s="0" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1"/>
       <c r="B404" s="0" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1"/>
       <c r="B405" s="0" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1"/>
       <c r="B406" s="0" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1"/>
       <c r="B407" s="0" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1"/>
       <c r="B408" s="0" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1"/>
       <c r="B409" s="0" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1"/>
-      <c r="B410" s="0" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="411">
       <c r="A411" s="1"/>
       <c r="B411" s="0" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1"/>
       <c r="B412" s="0" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1"/>
       <c r="B413" s="0" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1"/>
       <c r="B414" s="0" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1"/>
       <c r="B415" s="0" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1"/>
       <c r="B416" s="0" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1"/>
       <c r="B417" s="0" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1"/>
       <c r="B418" s="0" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1"/>
       <c r="B419" s="0" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1"/>
       <c r="B420" s="0" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1"/>
       <c r="B421" s="0" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1"/>
       <c r="B422" s="0" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1"/>
       <c r="B423" s="0" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1"/>
       <c r="B424" s="0" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1"/>
       <c r="B425" s="0" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1"/>
       <c r="B426" s="0" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1"/>
       <c r="B427" s="0" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1"/>
       <c r="B428" s="0" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1"/>
       <c r="B429" s="0" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1"/>
       <c r="B430" s="0" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1"/>
       <c r="B431" s="0" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1"/>
       <c r="B432" s="0" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1"/>
       <c r="B433" s="0" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1"/>
       <c r="B434" s="0" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1"/>
       <c r="B435" s="0" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1"/>
       <c r="B436" s="0" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1"/>
       <c r="B437" s="0" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1"/>
       <c r="B438" s="0" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1"/>
       <c r="B439" s="0" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1"/>
       <c r="B440" s="0" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1"/>
       <c r="B441" s="0" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1"/>
       <c r="B442" s="0" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1"/>
       <c r="B443" s="0" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1"/>
       <c r="B444" s="0" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1"/>
       <c r="B445" s="0" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1"/>
       <c r="B446" s="0" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1"/>
       <c r="B447" s="0" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1"/>
       <c r="B448" s="0" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1"/>
       <c r="B449" s="0" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1"/>
       <c r="B450" s="0" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1"/>
       <c r="B451" s="0" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="1"/>
       <c r="B452" s="0" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1"/>
       <c r="B453" s="0" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1"/>
       <c r="B454" s="0" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1"/>
       <c r="B455" s="0" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1"/>
       <c r="B456" s="0" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1"/>
       <c r="B457" s="0" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1"/>
       <c r="B458" s="0" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1"/>
       <c r="B459" s="0" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="1"/>
       <c r="B460" s="0" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1"/>
       <c r="B461" s="0" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1"/>
       <c r="B462" s="0" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1"/>
       <c r="B463" s="0" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1"/>
       <c r="B464" s="0" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1"/>
       <c r="B465" s="0" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1"/>
       <c r="B466" s="0" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="1"/>
       <c r="B467" s="0" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1"/>
       <c r="B468" s="0" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1"/>
       <c r="B469" s="0" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1"/>
       <c r="B470" s="0" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1"/>
       <c r="B471" s="0" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1"/>
       <c r="B472" s="0" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1"/>
       <c r="B473" s="0" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="1"/>
       <c r="B474" s="0" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1"/>
       <c r="B475" s="0" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1"/>
       <c r="B476" s="0" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1"/>
       <c r="B477" s="0" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1"/>
       <c r="B478" s="0" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="1"/>
       <c r="B479" s="0" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1"/>
       <c r="B480" s="0" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1"/>
       <c r="B481" s="0" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1"/>
       <c r="B482" s="0" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1"/>
       <c r="B483" s="0" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="1"/>
       <c r="B484" s="0" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="1"/>
       <c r="B485" s="0" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1"/>
       <c r="B486" s="0" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1"/>
       <c r="B487" s="0" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1"/>
       <c r="B488" s="0" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1"/>
       <c r="B489" s="0" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1"/>
       <c r="B490" s="0" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="1"/>
       <c r="B491" s="0" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1"/>
       <c r="B492" s="0" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1"/>
       <c r="B493" s="0" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="1"/>
       <c r="B494" s="0" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1"/>
       <c r="B495" s="0" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1"/>
       <c r="B496" s="0" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1"/>
       <c r="B497" s="0" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="1"/>
       <c r="B498" s="0" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1"/>
       <c r="B499" s="0" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1"/>
       <c r="B500" s="0" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="1"/>
       <c r="B501" s="0" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="1"/>
       <c r="B502" s="0" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="1"/>
       <c r="B503" s="0" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="1"/>
       <c r="B504" s="0" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1"/>
       <c r="B505" s="0" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="1"/>
       <c r="B506" s="0" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="1"/>
       <c r="B507" s="0" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="1"/>
       <c r="B508" s="0" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="1"/>
       <c r="B509" s="0" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="1"/>
       <c r="B510" s="0" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="1"/>
       <c r="B511" s="0" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1"/>
       <c r="B512" s="0" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="1"/>
       <c r="B513" s="0" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="1"/>
       <c r="B514" s="0" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="1"/>
       <c r="B515" s="0" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="1"/>
       <c r="B516" s="0" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="1"/>
       <c r="B517" s="0" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="1"/>
       <c r="B518" s="0" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="1"/>
       <c r="B519" s="0" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="1"/>
       <c r="B520" s="0" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="1"/>
       <c r="B521" s="0" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="1"/>
       <c r="B522" s="0" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="1"/>
       <c r="B523" s="0" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="1"/>
       <c r="B524" s="0" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1"/>
       <c r="B525" s="0" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="1"/>
       <c r="B526" s="0" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1"/>
       <c r="B527" s="0" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="1"/>
       <c r="B528" s="0" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="1"/>
       <c r="B529" s="0" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="1"/>
       <c r="B530" s="0" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="1"/>
       <c r="B531" s="0" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="1"/>
       <c r="B532" s="0" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="1"/>
       <c r="B533" s="0" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="1"/>
       <c r="B534" s="0" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="1"/>
       <c r="B535" s="0" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="1"/>
       <c r="B536" s="0" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="1"/>
       <c r="B537" s="0" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="1"/>
       <c r="B538" s="0" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="1"/>
       <c r="B539" s="0" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="1"/>
       <c r="B540" s="0" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="1"/>
       <c r="B541" s="0" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="1"/>
       <c r="B542" s="0" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="1"/>
       <c r="B543" s="0" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="1"/>
       <c r="B544" s="0" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="1"/>
       <c r="B545" s="0" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="1"/>
       <c r="B546" s="0" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="1"/>
       <c r="B547" s="0" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="1"/>
       <c r="B548" s="0" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="1"/>
       <c r="B549" s="0" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="1"/>
       <c r="B550" s="0" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="1"/>
       <c r="B551" s="0" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="1"/>
       <c r="B552" s="0" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="1"/>
       <c r="B553" s="0" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1"/>
       <c r="B554" s="0" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="1"/>
       <c r="B555" s="0" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="1"/>
       <c r="B556" s="0" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="1"/>
       <c r="B557" s="0" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="1"/>
       <c r="B558" s="0" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="1"/>
       <c r="B559" s="0" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="1"/>
       <c r="B560" s="0" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="1"/>
       <c r="B561" s="0" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="1"/>
       <c r="B562" s="0" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="1"/>
       <c r="B563" s="0" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="1"/>
       <c r="B564" s="0" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="1"/>
       <c r="B565" s="0" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="1"/>
       <c r="B566" s="0" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="1"/>
       <c r="B567" s="0" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="1"/>
       <c r="B568" s="0" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="1"/>
       <c r="B569" s="0" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="1"/>
       <c r="B570" s="0" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="1"/>
       <c r="B571" s="0" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="1"/>
       <c r="B572" s="0" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="1"/>
       <c r="B573" s="0" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="1"/>
       <c r="B574" s="0" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="1"/>
       <c r="B575" s="0" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="1"/>
       <c r="B576" s="0" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="1"/>
       <c r="B577" s="0" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="1"/>
       <c r="B578" s="0" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="1"/>
       <c r="B579" s="0" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="1"/>
       <c r="B580" s="0" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="1"/>
       <c r="B581" s="0" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="1"/>
       <c r="B582" s="0" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="1"/>
       <c r="B583" s="0" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="1"/>
       <c r="B584" s="0" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="1"/>
       <c r="B585" s="0" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="1"/>
       <c r="B586" s="0" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="1"/>
       <c r="B587" s="0" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="1"/>
       <c r="B588" s="0" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="1"/>
       <c r="B589" s="0" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="1"/>
       <c r="B590" s="0" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="1"/>
       <c r="B591" s="0" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="1"/>
       <c r="B592" s="0" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="1"/>
       <c r="B593" s="0" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="1"/>
       <c r="B594" s="0" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="1"/>
       <c r="B595" s="0" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="1"/>
       <c r="B596" s="0" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="1"/>
       <c r="B597" s="0" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="1"/>
       <c r="B598" s="0" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="1"/>
       <c r="B599" s="0" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="1"/>
       <c r="B600" s="0" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="1"/>
       <c r="B601" s="0" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="1"/>
       <c r="B602" s="0" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="1"/>
       <c r="B603" s="0" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="1"/>
       <c r="B604" s="0" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="1"/>
       <c r="B605" s="0" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="1"/>
       <c r="B606" s="0" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="1"/>
       <c r="B607" s="0" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="1"/>
       <c r="B608" s="0" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="1"/>
       <c r="B609" s="0" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="1"/>
       <c r="B610" s="0" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="1"/>
       <c r="B611" s="0" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="1"/>
       <c r="B612" s="0" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="1"/>
       <c r="B613" s="0" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="1"/>
       <c r="B614" s="0" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="1"/>
       <c r="B615" s="0" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="1"/>
       <c r="B616" s="0" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="1"/>
       <c r="B617" s="0" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="1"/>
       <c r="B618" s="0" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="1"/>
       <c r="B619" s="0" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="1"/>
       <c r="B620" s="0" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="1"/>
       <c r="B621" s="0" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="1"/>
       <c r="B622" s="0" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="1"/>
       <c r="B623" s="0" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="1"/>
       <c r="B624" s="0" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="1"/>
       <c r="B625" s="0" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="1"/>
       <c r="B626" s="0" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="1"/>
       <c r="B627" s="0" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="1"/>
       <c r="B628" s="0" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="1"/>
       <c r="B629" s="0" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="1"/>
       <c r="B630" s="0" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="1"/>
       <c r="B631" s="0" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="1"/>
       <c r="B632" s="0" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="1"/>
       <c r="B633" s="0" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="1"/>
       <c r="B634" s="0" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="1"/>
       <c r="B635" s="0" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="1"/>
       <c r="B636" s="0" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="1"/>
       <c r="B637" s="0" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="1"/>
       <c r="B638" s="0" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="1"/>
       <c r="B639" s="0" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="1"/>
       <c r="B640" s="0" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="1"/>
       <c r="B641" s="0" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="1"/>
       <c r="B642" s="0" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="1"/>
       <c r="B643" s="0" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="1"/>
       <c r="B644" s="0" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="1"/>
       <c r="B645" s="0" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="1"/>
       <c r="B646" s="0" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="1"/>
       <c r="B647" s="0" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="1"/>
       <c r="B648" s="0" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="1"/>
       <c r="B649" s="0" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="1"/>
       <c r="B650" s="0" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="1"/>
       <c r="B651" s="0" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="1"/>
       <c r="B652" s="0" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="1"/>
       <c r="B653" s="0" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="1"/>
       <c r="B654" s="0" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="1"/>
       <c r="B655" s="0" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="1"/>
       <c r="B656" s="0" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="1"/>
       <c r="B657" s="0" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="1"/>
       <c r="B658" s="0" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="1"/>
       <c r="B659" s="0" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="1"/>
       <c r="B660" s="0" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="1"/>
       <c r="B661" s="0" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="1"/>
       <c r="B662" s="0" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="1"/>
       <c r="B663" s="0" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="1"/>
       <c r="B664" s="0" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="1"/>
       <c r="B665" s="0" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="1"/>
       <c r="B666" s="0" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="1"/>
       <c r="B667" s="0" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="1"/>
       <c r="B668" s="0" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="1"/>
       <c r="B669" s="0" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="1"/>
       <c r="B670" s="0" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="1"/>
       <c r="B671" s="0" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="1"/>
       <c r="B672" s="0" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="1"/>
       <c r="B673" s="0" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="1"/>
       <c r="B674" s="0" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="1"/>
       <c r="B675" s="0" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="1"/>
       <c r="B676" s="0" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="1"/>
       <c r="B677" s="0" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="1"/>
       <c r="B678" s="0" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="1"/>
       <c r="B679" s="0" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="1"/>
       <c r="B680" s="0" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="1"/>
       <c r="B681" s="0" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="1"/>
       <c r="B682" s="0" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="1"/>
       <c r="B683" s="0" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="1"/>
       <c r="B684" s="0" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="1"/>
       <c r="B685" s="0" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="1"/>
       <c r="B686" s="0" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="1"/>
       <c r="B687" s="0" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="1"/>
       <c r="B688" s="0" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="1"/>
       <c r="B689" s="0" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="1"/>
       <c r="B690" s="0" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="1"/>
       <c r="B691" s="0" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="1"/>
       <c r="B692" s="0" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="1"/>
       <c r="B693" s="0" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="1"/>
       <c r="B694" s="0" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="1"/>
       <c r="B695" s="0" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="1"/>
       <c r="B696" s="0" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="1"/>
       <c r="B697" s="0" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" s="1"/>
       <c r="B698" s="0" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="1"/>
       <c r="B699" s="0" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="1"/>
       <c r="B700" s="0" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="1"/>
       <c r="B701" s="0" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="1"/>
       <c r="B702" s="0" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="1"/>
       <c r="B703" s="0" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="1"/>
       <c r="B704" s="0" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="1"/>
       <c r="B705" s="0" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="1"/>
       <c r="B706" s="0" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="1"/>
       <c r="B707" s="0" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="1"/>
       <c r="B708" s="0" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="1"/>
       <c r="B709" s="0" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="1"/>
       <c r="B710" s="0" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="1"/>
       <c r="B711" s="0" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="1"/>
       <c r="B712" s="0" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="1"/>
       <c r="B713" s="0" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="1"/>
       <c r="B714" s="0" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="1"/>
       <c r="B715" s="0" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="1"/>
       <c r="B716" s="0" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="1"/>
       <c r="B717" s="0" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" s="1"/>
       <c r="B718" s="0" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="1"/>
       <c r="B719" s="0" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="1"/>
       <c r="B720" s="0" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="1"/>
       <c r="B721" s="0" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="1"/>
       <c r="B722" s="0" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="1"/>
       <c r="B723" s="0" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="1"/>
       <c r="B724" s="0" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="1"/>
       <c r="B725" s="0" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" s="1"/>
       <c r="B726" s="0" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="1"/>
       <c r="B727" s="0" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="1"/>
       <c r="B728" s="0" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="1"/>
       <c r="B729" s="0" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="1"/>
       <c r="B730" s="0" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="1"/>
       <c r="B731" s="0" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="1"/>
       <c r="B732" s="0" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="1"/>
       <c r="B733" s="0" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="1"/>
       <c r="B734" s="0" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="1"/>
       <c r="B735" s="0" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" s="1"/>
       <c r="B736" s="0" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="1"/>
       <c r="B737" s="0" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="1"/>
       <c r="B738" s="0" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="1"/>
       <c r="B739" s="0" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" s="1"/>
       <c r="B740" s="0" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="1"/>
       <c r="B741" s="0" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="1"/>
       <c r="B742" s="0" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="1"/>
       <c r="B743" s="0" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" s="1"/>
       <c r="B744" s="0" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="1"/>
       <c r="B745" s="0" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="1"/>
       <c r="B746" s="0" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="1"/>
       <c r="B747" s="0" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="1"/>
       <c r="B748" s="0" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="1"/>
       <c r="B749" s="0" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="1"/>
       <c r="B750" s="0" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="1"/>
       <c r="B751" s="0" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="1"/>
       <c r="B752" s="0" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="1"/>
       <c r="B753" s="0" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="1"/>
       <c r="B754" s="0" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="1"/>
       <c r="B755" s="0" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="1"/>
       <c r="B756" s="0" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="1"/>
       <c r="B757" s="0" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="1"/>
       <c r="B758" s="0" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="1"/>
       <c r="B759" s="0" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="1"/>
       <c r="B760" s="0" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="1"/>
       <c r="B761" s="0" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="1"/>
       <c r="B762" s="0" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="1"/>
       <c r="B763" s="0" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="1"/>
       <c r="B764" s="0" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" s="1"/>
       <c r="B765" s="0" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" s="1"/>
       <c r="B766" s="0" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="1"/>
       <c r="B767" s="0" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="1"/>
       <c r="B768" s="0" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="1"/>
       <c r="B769" s="0" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="1"/>
       <c r="B770" s="0" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="1"/>
       <c r="B771" s="0" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" s="1"/>
       <c r="B772" s="0" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="1"/>
       <c r="B773" s="0" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="1"/>
       <c r="B774" s="0" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="1"/>
       <c r="B775" s="0" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="1"/>
       <c r="B776" s="0" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="1"/>
       <c r="B777" s="0" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" s="1"/>
       <c r="B778" s="0" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="1"/>
       <c r="B779" s="0" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="1"/>
       <c r="B780" s="0" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="1"/>
       <c r="B781" s="0" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="1"/>
       <c r="B782" s="0" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="1"/>
       <c r="B783" s="0" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="1"/>
       <c r="B784" s="0" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="1"/>
       <c r="B785" s="0" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" s="1"/>
       <c r="B786" s="0" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="1"/>
       <c r="B787" s="0" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" s="1"/>
       <c r="B788" s="0" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="1"/>
       <c r="B789" s="0" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="1"/>
       <c r="B790" s="0" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="1"/>
       <c r="B791" s="0" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" s="1"/>
       <c r="B792" s="0" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="1"/>
       <c r="B793" s="0" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" s="1"/>
       <c r="B794" s="0" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="1"/>
       <c r="B795" s="0" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="1"/>
       <c r="B796" s="0" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="1"/>
       <c r="B797" s="0" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="1"/>
       <c r="B798" s="0" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="1"/>
       <c r="B799" s="0" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="1"/>
       <c r="B800" s="0" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="1"/>
       <c r="B801" s="0" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="1"/>
       <c r="B802" s="0" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="1"/>
       <c r="B803" s="0" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="1"/>
       <c r="B804" s="0" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="1"/>
       <c r="B805" s="0" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="1"/>
       <c r="B806" s="0" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="1"/>
       <c r="B807" s="0" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="1"/>
       <c r="B808" s="0" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="1"/>
       <c r="B809" s="0" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="1"/>
       <c r="B810" s="0" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="1"/>
       <c r="B811" s="0" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="1"/>
       <c r="B812" s="0" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="1"/>
       <c r="B813" s="0" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="1"/>
       <c r="B814" s="0" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="1"/>
       <c r="B815" s="0" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="1"/>
       <c r="B816" s="0" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="1"/>
       <c r="B817" s="0" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="1"/>
       <c r="B818" s="0" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="1"/>
       <c r="B819" s="0" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="1"/>
       <c r="B820" s="0" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="1"/>
       <c r="B821" s="0" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="1"/>
       <c r="B822" s="0" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="1"/>
       <c r="B823" s="0" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="1"/>
       <c r="B824" s="0" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="1"/>
       <c r="B825" s="0" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="1"/>
       <c r="B826" s="0" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="1"/>
       <c r="B827" s="0" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="1"/>
       <c r="B828" s="0" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="1"/>
       <c r="B829" s="0" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="1"/>
       <c r="B830" s="0" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="1"/>
       <c r="B831" s="0" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" s="1"/>
       <c r="B832" s="0" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="1"/>
       <c r="B833" s="0" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="1"/>
       <c r="B834" s="0" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="1"/>
       <c r="B835" s="0" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" s="1"/>
       <c r="B836" s="0" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="1"/>
       <c r="B837" s="0" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="1"/>
       <c r="B838" s="0" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="1"/>
       <c r="B839" s="0" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="1"/>
       <c r="B840" s="0" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="1"/>
       <c r="B841" s="0" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="1"/>
       <c r="B842" s="0" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="1"/>
       <c r="B843" s="0" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="1"/>
       <c r="B844" s="0" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="1"/>
       <c r="B845" s="0" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="1"/>
       <c r="B846" s="0" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="1"/>
       <c r="B847" s="0" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="1"/>
       <c r="B848" s="0" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="1"/>
       <c r="B849" s="0" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="1"/>
       <c r="B850" s="0" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="1"/>
       <c r="B851" s="0" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="1"/>
       <c r="B852" s="0" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="1"/>
       <c r="B853" s="0" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="1"/>
       <c r="B854" s="0" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="1"/>
       <c r="B855" s="0" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="1"/>
       <c r="B856" s="0" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="1"/>
       <c r="B857" s="0" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="1"/>
       <c r="B858" s="0" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="1"/>
       <c r="B859" s="0" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="1"/>
       <c r="B860" s="0" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="1"/>
       <c r="B861" s="0" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="1"/>
       <c r="B862" s="0" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C862" s="0" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" s="1"/>
       <c r="B863" s="0" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="1"/>
       <c r="B864" s="0" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="1"/>
       <c r="B865" s="0" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="1"/>
       <c r="B866" s="0" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" s="1"/>
       <c r="B867" s="0" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
     </row>
     <row r="868">
@@ -9286,1310 +9238,1310 @@
     <row r="874">
       <c r="A874" s="1"/>
       <c r="B874" s="0" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="1"/>
       <c r="B875" s="0" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="1"/>
       <c r="B876" s="0" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="1"/>
       <c r="B877" s="0" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="1"/>
       <c r="B878" s="0" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" s="1"/>
       <c r="B879" s="0" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="1"/>
       <c r="B880" s="0" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="1"/>
       <c r="B881" s="0" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="1"/>
       <c r="B882" s="0" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="1"/>
       <c r="B883" s="0" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="1"/>
       <c r="B884" s="0" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="1"/>
       <c r="B885" s="0" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="1"/>
       <c r="B886" s="0" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="1"/>
       <c r="B887" s="0" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="1"/>
       <c r="B888" s="0" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="1"/>
       <c r="B889" s="0" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="1"/>
       <c r="B890" s="0" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="1"/>
       <c r="B891" s="0" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="1"/>
       <c r="B892" s="0" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="1"/>
       <c r="B893" s="0" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="1"/>
       <c r="B894" s="0" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="1"/>
       <c r="B895" s="0" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="1"/>
       <c r="B896" s="0" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="1"/>
       <c r="B897" s="0" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="1"/>
       <c r="B898" s="0" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="1"/>
       <c r="B899" s="0" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="1"/>
       <c r="B900" s="0" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="1"/>
       <c r="B901" s="0" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="1"/>
       <c r="B902" s="0" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="1"/>
       <c r="B903" s="0" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="1"/>
       <c r="B904" s="0" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="1"/>
       <c r="B905" s="0" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="1"/>
       <c r="B906" s="0" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="1"/>
       <c r="B907" s="0" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="1"/>
       <c r="B908" s="0" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="1"/>
       <c r="B909" s="0" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="1"/>
       <c r="B910" s="0" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="1"/>
       <c r="B911" s="0" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="1"/>
       <c r="B912" s="0" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="1"/>
       <c r="B913" s="0" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="1"/>
       <c r="B914" s="0" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="1"/>
       <c r="B915" s="0" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="1"/>
       <c r="B916" s="0" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="1"/>
       <c r="B917" s="0" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="1"/>
       <c r="B918" s="0" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="C918" s="0" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
     </row>
     <row r="919">
       <c r="B919" s="0" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="C919" s="0" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
     </row>
     <row r="920">
       <c r="B920" s="0" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C920" s="0" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
     </row>
     <row r="921">
       <c r="B921" s="0" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="C921" s="0" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
     </row>
     <row r="922">
       <c r="B922" s="0" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="C922" s="0" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
     </row>
     <row r="923">
       <c r="B923" s="0" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="C923" s="0" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
     </row>
     <row r="924">
       <c r="B924" s="0" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C924" s="0" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="925">
       <c r="B925" s="0" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="C925" s="0" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
     </row>
     <row r="926">
       <c r="B926" s="0" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="C926" s="0" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
     </row>
     <row r="927">
       <c r="B927" s="0" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="C927" s="0" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
     </row>
     <row r="928">
       <c r="B928" s="0" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="C928" s="0" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
     </row>
     <row r="929">
       <c r="B929" s="0" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="C929" s="0" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="930">
       <c r="B930" s="0" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="C930" s="0" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
     </row>
     <row r="931">
       <c r="B931" s="0" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C931" s="0" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
     </row>
     <row r="932">
       <c r="B932" s="0" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
       <c r="C932" s="0" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
     </row>
     <row r="933">
       <c r="B933" s="0" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="C933" s="0" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
     </row>
     <row r="934">
       <c r="B934" s="0" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="C934" s="0" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
     </row>
     <row r="935">
       <c r="B935" s="0" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="C935" s="0" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
     </row>
     <row r="936">
       <c r="B936" s="0" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="C936" s="0" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
     </row>
     <row r="937">
       <c r="B937" s="0" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
       <c r="C937" s="0" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
     </row>
     <row r="938">
       <c r="B938" s="0" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="C938" s="0" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
     </row>
     <row r="939">
       <c r="B939" s="0" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="C939" s="0" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
     </row>
     <row r="940">
       <c r="B940" s="0" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="C940" s="0" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
     </row>
     <row r="941">
       <c r="B941" s="0" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="C941" s="0" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
     </row>
     <row r="942">
       <c r="B942" s="0" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="C942" s="0" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
     </row>
     <row r="943">
       <c r="B943" s="0" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="C943" s="0" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
     </row>
     <row r="944">
       <c r="B944" s="0" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="C944" s="0" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
     </row>
     <row r="945">
       <c r="B945" s="0" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="C945" s="0" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
     </row>
     <row r="946">
       <c r="B946" s="0" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="C946" s="0" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
     </row>
     <row r="947">
       <c r="B947" s="0" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C947" s="0" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
     </row>
     <row r="948">
       <c r="B948" s="0" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C948" s="0" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
     </row>
     <row r="949">
       <c r="B949" s="0" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C949" s="0" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
     </row>
     <row r="950">
       <c r="B950" s="0" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C950" s="0" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
     </row>
     <row r="951">
       <c r="B951" s="0" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="C951" s="0" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
     </row>
     <row r="952">
       <c r="B952" s="0" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="C952" s="0" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
     </row>
     <row r="953">
       <c r="B953" s="0" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C953" s="0" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
     </row>
     <row r="954">
       <c r="B954" s="0" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="C954" s="0" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
     </row>
     <row r="955">
       <c r="B955" s="0" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="C955" s="0" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
     </row>
     <row r="956">
       <c r="B956" s="0" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="C956" s="0" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="957">
       <c r="B957" s="0" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C957" s="0" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="958">
       <c r="B958" s="0" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="C958" s="0" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="959">
       <c r="B959" s="0" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="C959" s="0" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="960">
       <c r="B960" s="0" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="C960" s="0" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="961">
       <c r="B961" s="0" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="C961" s="0" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="962">
       <c r="B962" s="0" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="C962" s="0" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="963">
       <c r="B963" s="0" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="C963" s="0" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="964">
       <c r="B964" s="0" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="C964" s="0" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="965">
       <c r="B965" s="0" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="C965" s="0" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="966">
       <c r="B966" s="0" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="C966" s="0" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="967">
       <c r="B967" s="0" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="C967" s="0" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="968">
       <c r="B968" s="0" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="C968" s="0" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="969">
       <c r="B969" s="0" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="C969" s="0" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="970">
       <c r="B970" s="0" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C970" s="0" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="971">
       <c r="B971" s="0" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
       <c r="C971" s="0" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="972">
       <c r="B972" s="0" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
       <c r="C972" s="0" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="973">
       <c r="B973" s="0" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="C973" s="0" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="974">
       <c r="B974" s="0" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="C974" s="0" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="975">
       <c r="B975" s="0" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="C975" s="0" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="976">
       <c r="B976" s="0" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="C976" s="0" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="977">
       <c r="B977" s="0" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="C977" s="0" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="978">
       <c r="B978" s="0" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
       <c r="C978" s="0" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="979">
       <c r="B979" s="0" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="C979" s="0" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="980">
       <c r="B980" s="0" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="C980" s="0" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="981">
       <c r="B981" s="0" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
       <c r="C981" s="0" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="982">
       <c r="B982" s="0" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="C982" s="0" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="983">
       <c r="B983" s="0" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="C983" s="0" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="984">
       <c r="B984" s="0" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
       <c r="C984" s="0" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="985">
       <c r="B985" s="0" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="C985" s="0" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="986">
       <c r="B986" s="0" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
       <c r="C986" s="0" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="987">
       <c r="B987" s="0" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
       <c r="C987" s="0" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="988">
       <c r="B988" s="0" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
       <c r="C988" s="0" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="989">
       <c r="B989" s="0" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
       <c r="C989" s="0" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="990">
       <c r="B990" s="0" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
       <c r="C990" s="0" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="991">
       <c r="B991" s="0" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="C991" s="0" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="992">
       <c r="B992" s="0" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="C992" s="0" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="993">
       <c r="B993" s="0" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="C993" s="0" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="994">
       <c r="B994" s="0" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
       <c r="C994" s="0" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="995">
       <c r="B995" s="0" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
       <c r="C995" s="0" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="996">
       <c r="B996" s="0" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
       <c r="C996" s="0" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="997">
       <c r="B997" s="0" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C997" s="0" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="998">
       <c r="B998" s="0" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
       <c r="C998" s="0" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="999">
       <c r="B999" s="0" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="C999" s="0" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="1000">
       <c r="B1000" s="0" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
       <c r="C1000" s="0" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1001">
       <c r="B1001" s="0" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="C1001" s="0" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1002">
       <c r="B1002" s="0" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C1002" s="0" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="1003">
       <c r="B1003" s="0" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
       <c r="C1003" s="0" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="1004">
       <c r="B1004" s="0" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
       <c r="C1004" s="0" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1005">
       <c r="B1005" s="0" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
       <c r="C1005" s="0" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1006">
       <c r="B1006" s="0" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="C1006" s="0" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="1007">
       <c r="B1007" s="0" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="C1007" s="0" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="1008">
       <c r="B1008" s="0" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
       <c r="C1008" s="0" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="1009">
       <c r="B1009" s="0" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="C1009" s="0" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="1010">
       <c r="B1010" s="0" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
       <c r="C1010" s="0" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="1011">
       <c r="B1011" s="0" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
       <c r="C1011" s="0" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="1012">
       <c r="B1012" s="0" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
       <c r="C1012" s="0" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="1013">
       <c r="B1013" s="0" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1014">
       <c r="B1014" s="0" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="1015">
       <c r="B1015" s="0" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1016">
       <c r="B1016" s="0" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1017">
       <c r="B1017" s="0" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1018">
       <c r="B1018" s="0" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1019">
       <c r="B1019" s="0" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1020">
       <c r="B1020" s="0" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
       <c r="C1020" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1021">
       <c r="B1021" s="0" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
       <c r="C1021" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1022">
       <c r="B1022" s="0" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
       <c r="C1022" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1023">
       <c r="B1023" s="0" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
       <c r="C1023" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1024">
       <c r="B1024" s="0" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="C1024" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1025">
       <c r="B1025" s="0" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
       <c r="C1025" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1026">
       <c r="B1026" s="0" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="1027">
       <c r="B1027" s="0" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1028">
       <c r="B1028" s="0" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="1029">
       <c r="B1029" s="0" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1030">
       <c r="B1030" s="0" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="1031">
       <c r="B1031" s="0" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="1032">
       <c r="B1032" s="0" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="1033">
       <c r="B1033" s="0" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="1034">
       <c r="B1034" s="0" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="1035">
       <c r="B1035" s="0" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="1036">
       <c r="B1036" s="0" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="1037">
       <c r="B1037" s="0" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="1038">
       <c r="B1038" s="0" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="1039">
       <c r="B1039" s="0" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="1040">
       <c r="B1040" s="0" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="1041">
       <c r="B1041" s="0" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="1042">
       <c r="B1042" s="0" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="1043">
       <c r="B1043" s="0" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="1044">
       <c r="B1044" s="0" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="1045">
       <c r="B1045" s="0" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="1046">
       <c r="B1046" s="0" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1047">
       <c r="B1047" s="0" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="1048">
       <c r="B1048" s="0" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1049">
       <c r="B1049" s="0" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1050">
       <c r="B1050" s="0" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="1051">
       <c r="B1051" s="0" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="1052">
       <c r="B1052" s="0" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="1053">
       <c r="B1053" s="0" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="1054">
       <c r="B1054" s="0" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="1055">
       <c r="B1055" s="0" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
       <c r="C1055" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1056">
       <c r="B1056" s="0" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="C1056" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1057">
       <c r="B1057" s="0" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
       <c r="C1057" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1058">
       <c r="B1058" s="0" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
       <c r="C1058" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1059">
       <c r="B1059" s="0" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
       <c r="C1059" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1060">
       <c r="B1060" s="0" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
       <c r="C1060" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="1061">
       <c r="B1061" s="0" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
       <c r="C1061" s="0" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -105,7 +105,7 @@
     <t>Buil_Desc_HarvestStation</t>
   </si>
   <si>
-    <t>Buil_Desc_InsuranceOffice</t>
+    <t>Buil_Desc_SupplyStation</t>
   </si>
   <si>
     <t>Buil_Desc_InterviewRoom</t>
@@ -114,13 +114,13 @@
     <t>Buil_Desc_MeatRack</t>
   </si>
   <si>
-    <t>Buil_Desc_MeatStall</t>
+    <t>Buil_Desc_FreshMarket</t>
   </si>
   <si>
     <t>Buil_Desc_MiningRig</t>
   </si>
   <si>
-    <t>Buil_Desc_Monitor</t>
+    <t>Buil_Desc_DDoSDevice</t>
   </si>
   <si>
     <t>Buil_Desc_NavStation</t>
@@ -135,7 +135,7 @@
     <t>Buil_Desc_OtakuDesk</t>
   </si>
   <si>
-    <t>Buil_Desc_ParcelLocker</t>
+    <t>Buil_Desc_PackageRack</t>
   </si>
   <si>
     <t>Buil_Desc_Pharmacy</t>
@@ -162,7 +162,7 @@
     <t>Buil_Desc_ResearchCenter</t>
   </si>
   <si>
-    <t>Buil_Desc_Restroom</t>
+    <t>Buil_Desc_Residence</t>
   </si>
   <si>
     <t>Buil_Desc_RoseBush</t>
@@ -174,7 +174,7 @@
     <t>Buil_Desc_ServerRoom</t>
   </si>
   <si>
-    <t>Buil_Desc_ServiceDesk</t>
+    <t>Buil_Desc_ComplaintsDepartment</t>
   </si>
   <si>
     <t>Buil_Desc_ShearsRack</t>
@@ -186,7 +186,7 @@
     <t>Buil_Desc_SortingCenter</t>
   </si>
   <si>
-    <t>Buil_Desc_SortingTable</t>
+    <t>Buil_Desc_CampfireGrill</t>
   </si>
   <si>
     <t>Buil_Desc_SouthernMoon</t>
@@ -225,7 +225,7 @@
     <t>Buil_Desc_Trap</t>
   </si>
   <si>
-    <t>Buil_Desc_TrophyRack</t>
+    <t>Buil_Desc_ThemeStatue</t>
   </si>
   <si>
     <t>Buil_Desc_VendingMachine</t>
@@ -309,7 +309,7 @@
     <t>Buil_Name_HarvestStation</t>
   </si>
   <si>
-    <t>Buil_Name_InsuranceOffice</t>
+    <t>Buil_Name_SupplyStation</t>
   </si>
   <si>
     <t>Buil_Name_InterviewRoom</t>
@@ -318,13 +318,13 @@
     <t>Buil_Name_MeatRack</t>
   </si>
   <si>
-    <t>Buil_Name_MeatStall</t>
+    <t>Buil_Name_FreshMarket</t>
   </si>
   <si>
     <t>Buil_Name_MiningRig</t>
   </si>
   <si>
-    <t>Buil_Name_Monitor</t>
+    <t>Buil_Name_DDoSDevice</t>
   </si>
   <si>
     <t>Buil_Name_NavStation</t>
@@ -339,7 +339,7 @@
     <t>Buil_Name_OtakuDesk</t>
   </si>
   <si>
-    <t>Buil_Name_ParcelLocker</t>
+    <t>Buil_Name_PackageRack</t>
   </si>
   <si>
     <t>Buil_Name_Pharmacy</t>
@@ -366,7 +366,7 @@
     <t>Buil_Name_ResearchCenter</t>
   </si>
   <si>
-    <t>Buil_Name_Restroom</t>
+    <t>Buil_Name_Residence</t>
   </si>
   <si>
     <t>Buil_Name_RoseBush</t>
@@ -378,7 +378,7 @@
     <t>Buil_Name_ServerRoom</t>
   </si>
   <si>
-    <t>Buil_Name_ServiceDesk</t>
+    <t>Buil_Name_ComplaintsDepartment</t>
   </si>
   <si>
     <t>Buil_Name_ShearsRack</t>
@@ -390,7 +390,7 @@
     <t>Buil_Name_SortingCenter</t>
   </si>
   <si>
-    <t>Buil_Name_SortingTable</t>
+    <t>Buil_Name_CampfireGrill</t>
   </si>
   <si>
     <t>Buil_Name_SouthernMoon</t>
@@ -429,7 +429,7 @@
     <t>Buil_Name_Trap</t>
   </si>
   <si>
-    <t>Buil_Name_TrophyRack</t>
+    <t>Buil_Name_ThemeStatue</t>
   </si>
   <si>
     <t>Buil_Name_VendingMachine</t>
@@ -714,6 +714,9 @@
     <t>LvTag_Desc_BlockingTechnique</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>LvTag_Desc_Conductor</t>
   </si>
   <si>
@@ -1458,16 +1461,16 @@
     <t>상점</t>
   </si>
   <si>
-    <t>Skill_Desc_BladeDance</t>
+    <t>Skill_Desc_InsatiableThirst</t>
   </si>
   <si>
     <t>Skill_Desc_Cheer Squad</t>
   </si>
   <si>
-    <t>Skill_Desc_Disarm</t>
-  </si>
-  <si>
-    <t>Skill_Desc_FireDrill</t>
+    <t>Skill_Desc_RiotArmor</t>
+  </si>
+  <si>
+    <t>Skill_Desc_ForgedInFire</t>
   </si>
   <si>
     <t>Skill_Desc_GiantSlayer</t>
@@ -1479,7 +1482,7 @@
     <t>Skill_Desc_JustPassingBy</t>
   </si>
   <si>
-    <t>Skill_Desc_LightLoad</t>
+    <t>Skill_Desc_ExpressDelivery</t>
   </si>
   <si>
     <t>Skill_Desc_NeatAndTidy</t>
@@ -1488,16 +1491,16 @@
     <t>Skill_Desc_UrgentRequest</t>
   </si>
   <si>
-    <t>Skill_Name_BladeDance</t>
+    <t>Skill_Name_InsatiableThirst</t>
   </si>
   <si>
     <t>Skill_Name_Cheer Squad</t>
   </si>
   <si>
-    <t>Skill_Name_Disarm</t>
-  </si>
-  <si>
-    <t>Skill_Name_FireDrill</t>
+    <t>Skill_Name_RiotArmor</t>
+  </si>
+  <si>
+    <t>Skill_Name_ForgedInFire</t>
   </si>
   <si>
     <t>Skill_Name_GiantSlayer</t>
@@ -1509,7 +1512,7 @@
     <t>Skill_Name_JustPassingBy</t>
   </si>
   <si>
-    <t>Skill_Name_LightLoad</t>
+    <t>Skill_Name_ExpressDelivery</t>
   </si>
   <si>
     <t>Skill_Name_NeatAndTidy</t>
@@ -1692,10 +1695,10 @@
     <t>Tech_Desc_Buil_HarvestStation_Lv3</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_InsuranceOffice_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_InsuranceOffice_Lv3</t>
+    <t>Tech_Desc_Buil_SupplyStation_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_SupplyStation_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_InterviewRoom_Lv2</t>
@@ -1710,10 +1713,10 @@
     <t>Tech_Desc_Buil_MeatRack_Lv3</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_MeatStall_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_MeatStall_Lv3</t>
+    <t>Tech_Desc_Buil_FreshMarket_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_FreshMarket_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_MiningRig_Lv2</t>
@@ -1722,10 +1725,10 @@
     <t>Tech_Desc_Buil_MiningRig_Lv3</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_Monitor_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_Monitor_Lv3</t>
+    <t>Tech_Desc_Buil_DDoSDevice_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_DDoSDevice_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_NavStation_Opt1</t>
@@ -1758,10 +1761,10 @@
     <t>Tech_Desc_Buil_OtakuDesk_Lv3</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_ParcelLocker_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_ParcelLocker_Lv3</t>
+    <t>Tech_Desc_Buil_PackageRack_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_PackageRack_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_Pharmacy_Lv2</t>
@@ -1824,10 +1827,10 @@
     <t>Tech_Desc_Buil_ResearchCenter_Lv3_Opt2</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_Restroom_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_Restroom_Lv3</t>
+    <t>Tech_Desc_Buil_Residence_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_Residence_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_RoseBush_Lv2</t>
@@ -1860,10 +1863,10 @@
     <t>Tech_Desc_Buil_ServerRoom_Opt4</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_ServiceDesk_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_ServiceDesk_Lv3</t>
+    <t>Tech_Desc_Buil_ComplaintsDepartment_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_ComplaintsDepartment_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_ShearsRack_Lv2</t>
@@ -1890,10 +1893,10 @@
     <t>Tech_Desc_Buil_SortingCenter_Lv3_Opt2</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_SortingTable_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_SortingTable_Lv3</t>
+    <t>Tech_Desc_Buil_CampfireGrill_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_CampfireGrill_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_SouthernMoon_Lv2</t>
@@ -1986,10 +1989,10 @@
     <t>Tech_Desc_Buil_Trap_Lv3</t>
   </si>
   <si>
-    <t>Tech_Desc_Buil_TrophyRack_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Desc_Buil_TrophyRack_Lv3</t>
+    <t>Tech_Desc_Buil_ThemeStatue_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Desc_Buil_ThemeStatue_Lv3</t>
   </si>
   <si>
     <t>Tech_Desc_Buil_VendingMachine_Lv2</t>
@@ -2190,10 +2193,10 @@
     <t>Tech_Name_Buil_HarvestStation_Lv3</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_InsuranceOffice_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_InsuranceOffice_Lv3</t>
+    <t>Tech_Name_Buil_SupplyStation_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_SupplyStation_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_InterviewRoom_Lv2</t>
@@ -2208,10 +2211,10 @@
     <t>Tech_Name_Buil_MeatRack_Lv3</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_MeatStall_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_MeatStall_Lv3</t>
+    <t>Tech_Name_Buil_FreshMarket_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_FreshMarket_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_MiningRig_Lv2</t>
@@ -2220,10 +2223,10 @@
     <t>Tech_Name_Buil_MiningRig_Lv3</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_Monitor_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_Monitor_Lv3</t>
+    <t>Tech_Name_Buil_DDoSDevice_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_DDoSDevice_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_NavStation_Opt1</t>
@@ -2256,10 +2259,10 @@
     <t>Tech_Name_Buil_OtakuDesk_Lv3</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_ParcelLocker_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_ParcelLocker_Lv3</t>
+    <t>Tech_Name_Buil_PackageRack_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_PackageRack_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_Pharmacy_Lv2</t>
@@ -2322,10 +2325,10 @@
     <t>Tech_Name_Buil_ResearchCenter_Lv3_Opt2</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_Restroom_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_Restroom_Lv3</t>
+    <t>Tech_Name_Buil_Residence_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_Residence_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_RoseBush_Lv2</t>
@@ -2358,10 +2361,10 @@
     <t>Tech_Name_Buil_ServerRoom_Opt4</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_ServiceDesk_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_ServiceDesk_Lv3</t>
+    <t>Tech_Name_Buil_ComplaintsDepartment_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_ComplaintsDepartment_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_ShearsRack_Lv2</t>
@@ -2388,10 +2391,10 @@
     <t>Tech_Name_Buil_SortingCenter_Lv3_Opt2</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_SortingTable_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_SortingTable_Lv3</t>
+    <t>Tech_Name_Buil_CampfireGrill_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_CampfireGrill_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_SouthernMoon_Lv2</t>
@@ -2484,10 +2487,10 @@
     <t>Tech_Name_Buil_Trap_Lv3</t>
   </si>
   <si>
-    <t>Tech_Name_Buil_TrophyRack_Lv2</t>
-  </si>
-  <si>
-    <t>Tech_Name_Buil_TrophyRack_Lv3</t>
+    <t>Tech_Name_Buil_ThemeStatue_Lv2</t>
+  </si>
+  <si>
+    <t>Tech_Name_Buil_ThemeStatue_Lv3</t>
   </si>
   <si>
     <t>Tech_Name_Buil_VendingMachine_Lv2</t>
@@ -3379,9 +3382,6 @@
   </si>
   <si>
     <t>LvEnter.Grade</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>LvEnter.CareerRecord.Button</t>
@@ -5367,4940 +5367,4982 @@
     </row>
     <row r="232">
       <c r="A232" s="1"/>
+      <c r="B232" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1"/>
       <c r="B233" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1"/>
       <c r="B234" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1"/>
       <c r="B235" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1"/>
       <c r="B236" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1"/>
       <c r="B237" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1"/>
       <c r="B238" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1"/>
       <c r="B239" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1"/>
       <c r="B240" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1"/>
       <c r="B241" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1"/>
       <c r="B242" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1"/>
       <c r="B243" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1"/>
       <c r="B244" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1"/>
+      <c r="B245" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1"/>
+      <c r="B246" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1"/>
       <c r="B247" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1"/>
       <c r="B248" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1"/>
       <c r="B249" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1"/>
       <c r="B250" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1"/>
       <c r="B251" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1"/>
       <c r="B252" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1"/>
       <c r="B253" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1"/>
       <c r="B254" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1"/>
       <c r="B255" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1"/>
       <c r="B256" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1"/>
       <c r="B257" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1"/>
       <c r="B258" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1"/>
       <c r="B259" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1"/>
       <c r="B260" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1"/>
       <c r="B261" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1"/>
       <c r="B262" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1"/>
       <c r="B263" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1"/>
       <c r="B264" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1"/>
       <c r="B265" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1"/>
       <c r="B266" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1"/>
       <c r="B267" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1"/>
       <c r="B268" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1"/>
       <c r="B269" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1"/>
       <c r="B270" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1"/>
       <c r="B271" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1"/>
       <c r="B272" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1"/>
       <c r="B273" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1"/>
       <c r="B274" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1"/>
       <c r="B275" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1"/>
       <c r="B276" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1"/>
       <c r="B277" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1"/>
       <c r="B278" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1"/>
       <c r="B279" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1"/>
       <c r="B280" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1"/>
       <c r="B281" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1"/>
       <c r="B282" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1"/>
       <c r="B283" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1"/>
       <c r="B284" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1"/>
       <c r="B285" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1"/>
       <c r="B286" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1"/>
       <c r="B287" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1"/>
       <c r="B288" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1"/>
       <c r="B289" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1"/>
       <c r="B290" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1"/>
       <c r="B291" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1"/>
       <c r="B292" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1"/>
       <c r="B293" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1"/>
       <c r="B294" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1"/>
       <c r="B295" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1"/>
       <c r="B296" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1"/>
       <c r="B297" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1"/>
       <c r="B298" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1"/>
       <c r="B299" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1"/>
       <c r="B300" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1"/>
       <c r="B301" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1"/>
       <c r="B302" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1"/>
       <c r="B303" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1"/>
       <c r="B304" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1"/>
+      <c r="B305" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1"/>
       <c r="B306" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1"/>
       <c r="B307" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1"/>
       <c r="B308" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1"/>
       <c r="B309" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1"/>
       <c r="B310" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1"/>
       <c r="B311" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1"/>
       <c r="B312" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1"/>
       <c r="B313" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1"/>
       <c r="B314" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1"/>
       <c r="B315" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1"/>
       <c r="B316" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1"/>
       <c r="B317" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1"/>
       <c r="B318" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1"/>
       <c r="B319" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1"/>
       <c r="B320" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1"/>
       <c r="B321" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1"/>
       <c r="B322" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1"/>
       <c r="B323" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1"/>
       <c r="B324" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1"/>
       <c r="B325" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1"/>
       <c r="B326" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1"/>
       <c r="B327" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1"/>
       <c r="B328" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1"/>
       <c r="B329" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1"/>
       <c r="B330" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1"/>
       <c r="B331" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1"/>
       <c r="B332" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1"/>
       <c r="B333" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1"/>
       <c r="B334" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1"/>
       <c r="B335" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1"/>
       <c r="B336" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1"/>
+      <c r="B337" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1"/>
       <c r="B338" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1"/>
       <c r="B339" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1"/>
       <c r="B340" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1"/>
       <c r="B341" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1"/>
       <c r="B342" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1"/>
       <c r="B343" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1"/>
       <c r="B344" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1"/>
       <c r="B345" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1"/>
       <c r="B346" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1"/>
       <c r="B347" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1"/>
       <c r="B348" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1"/>
       <c r="B349" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1"/>
+      <c r="B350" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1"/>
+      <c r="B351" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1"/>
       <c r="B352" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1"/>
       <c r="B353" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1"/>
       <c r="B354" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1"/>
       <c r="B355" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1"/>
       <c r="B356" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1"/>
       <c r="B357" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1"/>
       <c r="B358" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1"/>
       <c r="B359" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1"/>
       <c r="B360" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1"/>
       <c r="B361" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1"/>
       <c r="B362" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1"/>
       <c r="B363" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1"/>
       <c r="B364" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1"/>
       <c r="B365" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1"/>
       <c r="B366" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1"/>
       <c r="B367" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1"/>
       <c r="B368" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1"/>
       <c r="B369" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1"/>
       <c r="B370" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1"/>
       <c r="B371" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1"/>
       <c r="B372" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1"/>
       <c r="B373" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1"/>
       <c r="B374" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1"/>
       <c r="B375" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1"/>
       <c r="B376" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1"/>
       <c r="B377" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1"/>
       <c r="B378" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1"/>
       <c r="B379" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1"/>
       <c r="B380" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1"/>
       <c r="B381" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1"/>
       <c r="B382" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1"/>
       <c r="B383" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1"/>
       <c r="B384" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1"/>
       <c r="B385" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1"/>
       <c r="B386" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1"/>
       <c r="B387" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1"/>
       <c r="B388" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1"/>
       <c r="B389" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1"/>
       <c r="B390" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1"/>
       <c r="B391" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1"/>
       <c r="B392" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1"/>
       <c r="B393" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1"/>
       <c r="B394" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1"/>
       <c r="B395" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1"/>
       <c r="B396" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1"/>
       <c r="B397" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1"/>
       <c r="B398" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1"/>
       <c r="B399" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1"/>
       <c r="B400" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1"/>
       <c r="B401" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1"/>
       <c r="B402" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1"/>
       <c r="B403" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1"/>
       <c r="B404" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1"/>
       <c r="B405" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1"/>
       <c r="B406" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1"/>
       <c r="B407" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1"/>
       <c r="B408" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1"/>
       <c r="B409" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1"/>
+      <c r="B410" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1"/>
       <c r="B411" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1"/>
       <c r="B412" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1"/>
       <c r="B413" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1"/>
       <c r="B414" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1"/>
       <c r="B415" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1"/>
       <c r="B416" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1"/>
       <c r="B417" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1"/>
       <c r="B418" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1"/>
       <c r="B419" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1"/>
       <c r="B420" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1"/>
       <c r="B421" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1"/>
       <c r="B422" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1"/>
       <c r="B423" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1"/>
       <c r="B424" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1"/>
       <c r="B425" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1"/>
       <c r="B426" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1"/>
       <c r="B427" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1"/>
       <c r="B428" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1"/>
       <c r="B429" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1"/>
       <c r="B430" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1"/>
       <c r="B431" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1"/>
       <c r="B432" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1"/>
       <c r="B433" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1"/>
       <c r="B434" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1"/>
       <c r="B435" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1"/>
       <c r="B436" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1"/>
       <c r="B437" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1"/>
       <c r="B438" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1"/>
       <c r="B439" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1"/>
       <c r="B440" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1"/>
       <c r="B441" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1"/>
       <c r="B442" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1"/>
       <c r="B443" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1"/>
       <c r="B444" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1"/>
       <c r="B445" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1"/>
       <c r="B446" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1"/>
       <c r="B447" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1"/>
       <c r="B448" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1"/>
       <c r="B449" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1"/>
       <c r="B450" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1"/>
       <c r="B451" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="1"/>
       <c r="B452" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1"/>
       <c r="B453" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1"/>
       <c r="B454" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1"/>
       <c r="B455" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1"/>
       <c r="B456" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1"/>
       <c r="B457" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1"/>
       <c r="B458" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1"/>
       <c r="B459" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="1"/>
       <c r="B460" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1"/>
       <c r="B461" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1"/>
       <c r="B462" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1"/>
       <c r="B463" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1"/>
       <c r="B464" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1"/>
       <c r="B465" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1"/>
       <c r="B466" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="1"/>
       <c r="B467" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1"/>
       <c r="B468" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1"/>
       <c r="B469" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1"/>
       <c r="B470" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1"/>
       <c r="B471" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1"/>
       <c r="B472" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1"/>
       <c r="B473" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="1"/>
       <c r="B474" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1"/>
       <c r="B475" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1"/>
       <c r="B476" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1"/>
       <c r="B477" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1"/>
       <c r="B478" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="1"/>
       <c r="B479" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1"/>
       <c r="B480" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1"/>
       <c r="B481" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1"/>
       <c r="B482" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1"/>
       <c r="B483" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="1"/>
       <c r="B484" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="1"/>
       <c r="B485" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1"/>
       <c r="B486" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1"/>
       <c r="B487" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1"/>
       <c r="B488" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1"/>
       <c r="B489" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1"/>
       <c r="B490" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="1"/>
       <c r="B491" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1"/>
       <c r="B492" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1"/>
       <c r="B493" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="1"/>
       <c r="B494" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1"/>
       <c r="B495" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1"/>
       <c r="B496" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1"/>
       <c r="B497" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="1"/>
       <c r="B498" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1"/>
       <c r="B499" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1"/>
       <c r="B500" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="1"/>
       <c r="B501" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="1"/>
       <c r="B502" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="1"/>
       <c r="B503" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="1"/>
       <c r="B504" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1"/>
       <c r="B505" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="1"/>
       <c r="B506" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="1"/>
       <c r="B507" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="1"/>
       <c r="B508" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="1"/>
       <c r="B509" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="1"/>
       <c r="B510" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="1"/>
       <c r="B511" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1"/>
       <c r="B512" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="1"/>
       <c r="B513" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="1"/>
       <c r="B514" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="1"/>
       <c r="B515" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="1"/>
       <c r="B516" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="1"/>
       <c r="B517" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="1"/>
       <c r="B518" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="1"/>
       <c r="B519" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="1"/>
       <c r="B520" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="1"/>
       <c r="B521" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="1"/>
       <c r="B522" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="1"/>
       <c r="B523" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="1"/>
       <c r="B524" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1"/>
       <c r="B525" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="1"/>
       <c r="B526" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1"/>
       <c r="B527" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="1"/>
       <c r="B528" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="1"/>
       <c r="B529" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="1"/>
       <c r="B530" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="1"/>
       <c r="B531" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="1"/>
       <c r="B532" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="1"/>
       <c r="B533" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="1"/>
       <c r="B534" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="1"/>
       <c r="B535" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="1"/>
       <c r="B536" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="1"/>
       <c r="B537" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="1"/>
       <c r="B538" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="1"/>
       <c r="B539" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="1"/>
       <c r="B540" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="1"/>
       <c r="B541" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="1"/>
       <c r="B542" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="1"/>
       <c r="B543" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="1"/>
       <c r="B544" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="1"/>
       <c r="B545" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="1"/>
       <c r="B546" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="1"/>
       <c r="B547" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="1"/>
       <c r="B548" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="1"/>
       <c r="B549" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="1"/>
       <c r="B550" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="1"/>
       <c r="B551" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="1"/>
       <c r="B552" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="1"/>
       <c r="B553" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="1"/>
       <c r="B554" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="1"/>
       <c r="B555" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="1"/>
       <c r="B556" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="1"/>
       <c r="B557" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="1"/>
       <c r="B558" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="1"/>
       <c r="B559" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="1"/>
       <c r="B560" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="1"/>
       <c r="B561" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="1"/>
       <c r="B562" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="1"/>
       <c r="B563" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="1"/>
       <c r="B564" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="1"/>
       <c r="B565" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="1"/>
       <c r="B566" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="1"/>
       <c r="B567" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="1"/>
       <c r="B568" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="1"/>
       <c r="B569" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="1"/>
       <c r="B570" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="1"/>
       <c r="B571" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="1"/>
       <c r="B572" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="1"/>
       <c r="B573" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="1"/>
       <c r="B574" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="1"/>
       <c r="B575" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="1"/>
       <c r="B576" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="1"/>
       <c r="B577" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="1"/>
       <c r="B578" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="1"/>
       <c r="B579" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="1"/>
       <c r="B580" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="1"/>
       <c r="B581" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="1"/>
       <c r="B582" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="1"/>
       <c r="B583" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="1"/>
       <c r="B584" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="1"/>
       <c r="B585" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="1"/>
       <c r="B586" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="1"/>
       <c r="B587" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="1"/>
       <c r="B588" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="1"/>
       <c r="B589" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="1"/>
       <c r="B590" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="1"/>
       <c r="B591" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="1"/>
       <c r="B592" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="1"/>
       <c r="B593" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="1"/>
       <c r="B594" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="1"/>
       <c r="B595" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="1"/>
       <c r="B596" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="1"/>
       <c r="B597" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="1"/>
       <c r="B598" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="1"/>
       <c r="B599" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="1"/>
       <c r="B600" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="1"/>
       <c r="B601" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="1"/>
       <c r="B602" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="1"/>
       <c r="B603" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="1"/>
       <c r="B604" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="1"/>
       <c r="B605" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="1"/>
       <c r="B606" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="1"/>
       <c r="B607" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="1"/>
       <c r="B608" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="1"/>
       <c r="B609" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="1"/>
       <c r="B610" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="1"/>
       <c r="B611" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="1"/>
       <c r="B612" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="1"/>
       <c r="B613" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="1"/>
       <c r="B614" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="1"/>
       <c r="B615" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="1"/>
       <c r="B616" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="1"/>
       <c r="B617" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="1"/>
       <c r="B618" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="1"/>
       <c r="B619" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="1"/>
       <c r="B620" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="1"/>
       <c r="B621" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="1"/>
       <c r="B622" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="1"/>
       <c r="B623" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="1"/>
       <c r="B624" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="1"/>
       <c r="B625" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="1"/>
       <c r="B626" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="1"/>
       <c r="B627" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="1"/>
       <c r="B628" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="1"/>
       <c r="B629" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="1"/>
       <c r="B630" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="1"/>
       <c r="B631" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="1"/>
       <c r="B632" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="1"/>
       <c r="B633" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="1"/>
       <c r="B634" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="1"/>
       <c r="B635" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="1"/>
       <c r="B636" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="1"/>
       <c r="B637" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="1"/>
       <c r="B638" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="1"/>
       <c r="B639" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="1"/>
       <c r="B640" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="1"/>
       <c r="B641" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="1"/>
       <c r="B642" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="1"/>
       <c r="B643" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="1"/>
       <c r="B644" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="1"/>
       <c r="B645" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="1"/>
       <c r="B646" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="1"/>
       <c r="B647" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="1"/>
       <c r="B648" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="1"/>
       <c r="B649" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="1"/>
       <c r="B650" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="1"/>
       <c r="B651" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="1"/>
       <c r="B652" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="1"/>
       <c r="B653" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="1"/>
       <c r="B654" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="1"/>
       <c r="B655" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="1"/>
       <c r="B656" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="1"/>
       <c r="B657" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="1"/>
       <c r="B658" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="1"/>
       <c r="B659" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="1"/>
       <c r="B660" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="1"/>
       <c r="B661" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="1"/>
       <c r="B662" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="1"/>
       <c r="B663" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="1"/>
       <c r="B664" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="1"/>
       <c r="B665" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="1"/>
       <c r="B666" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="1"/>
       <c r="B667" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="1"/>
       <c r="B668" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="1"/>
       <c r="B669" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="1"/>
       <c r="B670" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="1"/>
       <c r="B671" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="1"/>
       <c r="B672" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="1"/>
       <c r="B673" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="1"/>
       <c r="B674" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="1"/>
       <c r="B675" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="1"/>
       <c r="B676" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="1"/>
       <c r="B677" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="1"/>
       <c r="B678" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="1"/>
       <c r="B679" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="1"/>
       <c r="B680" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="1"/>
       <c r="B681" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="1"/>
       <c r="B682" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="1"/>
       <c r="B683" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="1"/>
       <c r="B684" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="1"/>
       <c r="B685" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="1"/>
       <c r="B686" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="1"/>
       <c r="B687" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="1"/>
       <c r="B688" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="1"/>
       <c r="B689" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="1"/>
       <c r="B690" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="1"/>
       <c r="B691" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="1"/>
       <c r="B692" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="1"/>
       <c r="B693" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="1"/>
       <c r="B694" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="1"/>
       <c r="B695" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="1"/>
       <c r="B696" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="1"/>
       <c r="B697" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" s="1"/>
       <c r="B698" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="1"/>
       <c r="B699" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="1"/>
       <c r="B700" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="1"/>
       <c r="B701" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="1"/>
       <c r="B702" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="1"/>
       <c r="B703" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="1"/>
       <c r="B704" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="1"/>
       <c r="B705" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="1"/>
       <c r="B706" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="1"/>
       <c r="B707" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="1"/>
       <c r="B708" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="1"/>
       <c r="B709" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="1"/>
       <c r="B710" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="1"/>
       <c r="B711" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="1"/>
       <c r="B712" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="1"/>
       <c r="B713" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="1"/>
       <c r="B714" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="1"/>
       <c r="B715" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="1"/>
       <c r="B716" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="1"/>
       <c r="B717" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" s="1"/>
       <c r="B718" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="1"/>
       <c r="B719" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="1"/>
       <c r="B720" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="1"/>
       <c r="B721" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="1"/>
       <c r="B722" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="1"/>
       <c r="B723" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="1"/>
       <c r="B724" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="1"/>
       <c r="B725" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" s="1"/>
       <c r="B726" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="1"/>
       <c r="B727" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="1"/>
       <c r="B728" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="1"/>
       <c r="B729" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="1"/>
       <c r="B730" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="1"/>
       <c r="B731" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="1"/>
       <c r="B732" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="1"/>
       <c r="B733" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="1"/>
       <c r="B734" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="1"/>
       <c r="B735" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" s="1"/>
       <c r="B736" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="1"/>
       <c r="B737" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="1"/>
       <c r="B738" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="1"/>
       <c r="B739" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" s="1"/>
       <c r="B740" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="1"/>
       <c r="B741" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="1"/>
       <c r="B742" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="1"/>
       <c r="B743" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" s="1"/>
       <c r="B744" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="1"/>
       <c r="B745" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="1"/>
       <c r="B746" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="1"/>
       <c r="B747" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="1"/>
       <c r="B748" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="1"/>
       <c r="B749" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="1"/>
       <c r="B750" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="1"/>
       <c r="B751" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="1"/>
       <c r="B752" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="1"/>
       <c r="B753" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="1"/>
       <c r="B754" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="1"/>
       <c r="B755" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="1"/>
       <c r="B756" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="1"/>
       <c r="B757" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="1"/>
       <c r="B758" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="1"/>
       <c r="B759" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="1"/>
       <c r="B760" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="1"/>
       <c r="B761" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="1"/>
       <c r="B762" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="1"/>
       <c r="B763" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="1"/>
       <c r="B764" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" s="1"/>
       <c r="B765" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" s="1"/>
       <c r="B766" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="1"/>
       <c r="B767" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="1"/>
       <c r="B768" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="1"/>
       <c r="B769" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="1"/>
       <c r="B770" s="0" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="1"/>
       <c r="B771" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" s="1"/>
       <c r="B772" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="1"/>
       <c r="B773" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="1"/>
       <c r="B774" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="1"/>
       <c r="B775" s="0" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" s="1"/>
       <c r="B776" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="1"/>
       <c r="B777" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" s="1"/>
       <c r="B778" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="1"/>
       <c r="B779" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="1"/>
       <c r="B780" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="1"/>
       <c r="B781" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="1"/>
       <c r="B782" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="1"/>
       <c r="B783" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="1"/>
       <c r="B784" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="1"/>
       <c r="B785" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" s="1"/>
       <c r="B786" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="1"/>
       <c r="B787" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" s="1"/>
       <c r="B788" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="1"/>
       <c r="B789" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="1"/>
       <c r="B790" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="1"/>
       <c r="B791" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" s="1"/>
       <c r="B792" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="1"/>
       <c r="B793" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" s="1"/>
       <c r="B794" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="1"/>
       <c r="B795" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="1"/>
       <c r="B796" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="1"/>
       <c r="B797" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" s="1"/>
       <c r="B798" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="1"/>
       <c r="B799" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="1"/>
       <c r="B800" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="1"/>
       <c r="B801" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="1"/>
       <c r="B802" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="1"/>
       <c r="B803" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="1"/>
       <c r="B804" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="1"/>
       <c r="B805" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="1"/>
       <c r="B806" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="1"/>
       <c r="B807" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="1"/>
       <c r="B808" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="1"/>
       <c r="B809" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="1"/>
       <c r="B810" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="1"/>
       <c r="B811" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="1"/>
       <c r="B812" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="1"/>
       <c r="B813" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" s="1"/>
       <c r="B814" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="1"/>
       <c r="B815" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="1"/>
       <c r="B816" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="1"/>
       <c r="B817" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="1"/>
       <c r="B818" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="1"/>
       <c r="B819" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="1"/>
       <c r="B820" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="1"/>
       <c r="B821" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="1"/>
       <c r="B822" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="1"/>
       <c r="B823" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="1"/>
       <c r="B824" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="1"/>
       <c r="B825" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="1"/>
       <c r="B826" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="1"/>
       <c r="B827" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="1"/>
       <c r="B828" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="1"/>
       <c r="B829" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="1"/>
       <c r="B830" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="1"/>
       <c r="B831" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" s="1"/>
       <c r="B832" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="1"/>
       <c r="B833" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" s="1"/>
       <c r="B834" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="1"/>
       <c r="B835" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" s="1"/>
       <c r="B836" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="1"/>
       <c r="B837" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="1"/>
       <c r="B838" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="1"/>
       <c r="B839" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" s="1"/>
       <c r="B840" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="1"/>
       <c r="B841" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" s="1"/>
       <c r="B842" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="1"/>
       <c r="B843" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="1"/>
       <c r="B844" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="1"/>
       <c r="B845" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" s="1"/>
       <c r="B846" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="1"/>
       <c r="B847" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="1"/>
       <c r="B848" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="1"/>
       <c r="B849" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="1"/>
       <c r="B850" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="1"/>
       <c r="B851" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="1"/>
       <c r="B852" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="1"/>
       <c r="B853" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="1"/>
       <c r="B854" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="1"/>
       <c r="B855" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="1"/>
       <c r="B856" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="1"/>
       <c r="B857" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="1"/>
       <c r="B858" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" s="1"/>
       <c r="B859" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" s="1"/>
       <c r="B860" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="1"/>
       <c r="B861" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" s="1"/>
       <c r="B862" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C862" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" s="1"/>
       <c r="B863" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" s="1"/>
       <c r="B864" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" s="1"/>
       <c r="B865" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="1"/>
       <c r="B866" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" s="1"/>
       <c r="B867" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" s="1"/>
+      <c r="B868" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" s="1"/>
+      <c r="B869" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="1"/>
+      <c r="B870" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" s="1"/>
+      <c r="B871" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" s="1"/>
+      <c r="B872" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" s="1"/>
+      <c r="B873" s="0" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" s="1"/>
       <c r="B874" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="1"/>
       <c r="B875" s="0" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" s="1"/>
       <c r="B876" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="1"/>
       <c r="B877" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" s="1"/>
       <c r="B878" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" s="1"/>
       <c r="B879" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="1"/>
       <c r="B880" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" s="1"/>
       <c r="B881" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" s="1"/>
       <c r="B882" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="1"/>
       <c r="B883" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" s="1"/>
       <c r="B884" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" s="1"/>
       <c r="B885" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="1"/>
       <c r="B886" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" s="1"/>
       <c r="B887" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" s="1"/>
       <c r="B888" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="1"/>
       <c r="B889" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="1"/>
       <c r="B890" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" s="1"/>
       <c r="B891" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" s="1"/>
       <c r="B892" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" s="1"/>
       <c r="B893" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" s="1"/>
       <c r="B894" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="1"/>
       <c r="B895" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" s="1"/>
       <c r="B896" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" s="1"/>
       <c r="B897" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="1"/>
       <c r="B898" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" s="1"/>
       <c r="B899" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" s="1"/>
       <c r="B900" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="1"/>
       <c r="B901" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="1"/>
       <c r="B902" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" s="1"/>
       <c r="B903" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" s="1"/>
       <c r="B904" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" s="1"/>
       <c r="B905" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" s="1"/>
       <c r="B906" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="1"/>
       <c r="B907" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="1"/>
       <c r="B908" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="1"/>
       <c r="B909" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="1"/>
       <c r="B910" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="1"/>
       <c r="B911" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="1"/>
       <c r="B912" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="1"/>
       <c r="B913" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="1"/>
       <c r="B914" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" s="1"/>
       <c r="B915" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="1"/>
       <c r="B916" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" s="1"/>
       <c r="B917" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" s="1"/>
       <c r="B918" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C918" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="919">
       <c r="B919" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C919" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="920">
       <c r="B920" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C920" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="921">
       <c r="B921" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C921" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="922">
       <c r="B922" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C922" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="923">
       <c r="B923" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C923" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="924">
       <c r="B924" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C924" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="925">
       <c r="B925" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C925" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="926">
       <c r="B926" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C926" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="927">
       <c r="B927" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C927" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="928">
       <c r="B928" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C928" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="929">
       <c r="B929" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C929" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="930">
       <c r="B930" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C930" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="931">
       <c r="B931" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C931" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="932">
       <c r="B932" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C932" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="933">
       <c r="B933" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C933" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="934">
       <c r="B934" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C934" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="935">
       <c r="B935" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C935" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="936">
       <c r="B936" s="0" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C936" s="0" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="937">
       <c r="B937" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C937" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="938">
       <c r="B938" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C938" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="939">
       <c r="B939" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C939" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="940">
       <c r="B940" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C940" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="941">
       <c r="B941" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C941" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="942">
       <c r="B942" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C942" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="943">
       <c r="B943" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C943" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="944">
       <c r="B944" s="0" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C944" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="945">
       <c r="B945" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C945" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="946">
       <c r="B946" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C946" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="947">
       <c r="B947" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C947" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="948">
       <c r="B948" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C948" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="949">
       <c r="B949" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C949" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="950">
       <c r="B950" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C950" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="951">
       <c r="B951" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C951" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="952">
       <c r="B952" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C952" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="953">
       <c r="B953" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C953" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="954">
       <c r="B954" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C954" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="955">
       <c r="B955" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C955" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="956">
       <c r="B956" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C956" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="957">
       <c r="B957" s="0" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C957" s="0" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="958">
       <c r="B958" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C958" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="959">
       <c r="B959" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C959" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="960">
       <c r="B960" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C960" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="961">
       <c r="B961" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C961" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="962">
       <c r="B962" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C962" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="963">
       <c r="B963" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C963" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="964">
       <c r="B964" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C964" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="965">
       <c r="B965" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C965" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="966">
       <c r="B966" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C966" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="967">
       <c r="B967" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C967" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="968">
       <c r="B968" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C968" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="969">
       <c r="B969" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C969" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="970">
       <c r="B970" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C970" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="971">
       <c r="B971" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C971" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="972">
       <c r="B972" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C972" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="973">
       <c r="B973" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C973" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="974">
       <c r="B974" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C974" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="975">
       <c r="B975" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C975" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="976">
       <c r="B976" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C976" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="977">
       <c r="B977" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C977" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="978">
       <c r="B978" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C978" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="979">
       <c r="B979" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C979" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="980">
       <c r="B980" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C980" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="981">
       <c r="B981" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C981" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="982">
       <c r="B982" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C982" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="983">
       <c r="B983" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C983" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="984">
       <c r="B984" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C984" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="985">
       <c r="B985" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C985" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="986">
       <c r="B986" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C986" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="987">
       <c r="B987" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C987" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="988">
       <c r="B988" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C988" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="989">
       <c r="B989" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C989" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="990">
       <c r="B990" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C990" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="991">
       <c r="B991" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C991" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="992">
       <c r="B992" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C992" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="993">
       <c r="B993" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C993" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="994">
       <c r="B994" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C994" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="995">
       <c r="B995" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C995" s="0" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="996">
       <c r="B996" s="0" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C996" s="0" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="997">
       <c r="B997" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C997" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="998">
       <c r="B998" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C998" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="999">
       <c r="B999" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C999" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1000">
       <c r="B1000" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C1000" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1001">
       <c r="B1001" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C1001" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1002">
       <c r="B1002" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C1002" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1003">
       <c r="B1003" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C1003" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1004">
       <c r="B1004" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C1004" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1005">
       <c r="B1005" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C1005" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="1006">
       <c r="B1006" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C1006" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="1007">
       <c r="B1007" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C1007" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="1008">
       <c r="B1008" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C1008" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="1009">
       <c r="B1009" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C1009" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="1010">
       <c r="B1010" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C1010" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="1011">
       <c r="B1011" s="0" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C1011" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="1012">
       <c r="B1012" s="0" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C1012" s="0" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1013">
       <c r="B1013" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="1014">
       <c r="B1014" s="0" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1015">
       <c r="B1015" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1016">
       <c r="B1016" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="1017">
       <c r="B1017" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="1018">
       <c r="B1018" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="1019">
       <c r="B1019" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="1020">
       <c r="B1020" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C1020" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1021">
@@ -10308,7 +10350,7 @@
         <v>1123</v>
       </c>
       <c r="C1021" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1022">
@@ -10316,7 +10358,7 @@
         <v>1124</v>
       </c>
       <c r="C1022" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1023">
@@ -10324,7 +10366,7 @@
         <v>1125</v>
       </c>
       <c r="C1023" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1024">
@@ -10332,7 +10374,7 @@
         <v>1126</v>
       </c>
       <c r="C1024" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1025">
@@ -10340,7 +10382,7 @@
         <v>1127</v>
       </c>
       <c r="C1025" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1026">
@@ -10493,7 +10535,7 @@
         <v>1157</v>
       </c>
       <c r="C1055" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1056">
@@ -10501,7 +10543,7 @@
         <v>1158</v>
       </c>
       <c r="C1056" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1057">
@@ -10509,7 +10551,7 @@
         <v>1159</v>
       </c>
       <c r="C1057" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1058">
@@ -10517,7 +10559,7 @@
         <v>1160</v>
       </c>
       <c r="C1058" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1059">
@@ -10525,7 +10567,7 @@
         <v>1161</v>
       </c>
       <c r="C1059" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1060">
@@ -10533,7 +10575,7 @@
         <v>1162</v>
       </c>
       <c r="C1060" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
     <row r="1061">
@@ -10541,7 +10583,7 @@
         <v>1163</v>
       </c>
       <c r="C1061" s="0" t="s">
-        <v>1122</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Languages/Korean.xlsx
+++ b/AAAGameData/Languages/Korean.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="1180">
   <si>
     <t>Archetype.Butchery</t>
   </si>
@@ -3544,6 +3544,15 @@
   </si>
   <si>
     <t>한 칸씩 건설하며 상하좌우로 연결된 벽은 총 체력을 공유합니다.</t>
+  </si>
+  <si>
+    <t>Skill_Name_Sweep</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Skill_Desc_Sweep</t>
   </si>
 </sst>
 </file>
@@ -4004,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1068"/>
+  <dimension ref="A1:C1070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.1796875" customWidth="1"/>
@@ -10600,6 +10609,22 @@
         <v>1176</v>
       </c>
     </row>
+    <row r="1069">
+      <c r="B1069" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C1069" s="0" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="B1070" s="0" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C1070" s="0" t="s">
+        <v>1178</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
